--- a/examples/interwar_poland/market_access/outputs/checks/unit_weighted_domestic_access_change_1938_vs_1924.xlsx
+++ b/examples/interwar_poland/market_access/outputs/checks/unit_weighted_domestic_access_change_1938_vs_1924.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F495"/>
+  <dimension ref="A1:J495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,26 @@
           <t>proportional_change_1938_vs_1924</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>avg_inverse_distance_1924</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>avg_inverse_distance_1938</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>avg_inverse_distance_change_ratio_1938_vs_1924</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>avg_inverse_distance_proportional_change_1938_vs_1924</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,6 +503,18 @@
       <c r="F2" t="n">
         <v>0.04984375688186349</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.003529727028549723</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.003586997955553443</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.016225313328904</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.01622531332890366</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -507,6 +539,18 @@
       <c r="F3" t="n">
         <v>0.03577977506890712</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.003977064595392107</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.004019392839368576</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.010643086870028</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01064308687002765</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,6 +575,18 @@
       <c r="F4" t="n">
         <v>0.1220194117155483</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.00543499873645822</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.005757823424894984</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.059397380586538</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.05939738058653844</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -555,6 +611,18 @@
       <c r="F5" t="n">
         <v>0.05908824798848666</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.005208684538144874</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0052814667024042</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.013973233304171</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.01397323330417093</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -579,6 +647,18 @@
       <c r="F6" t="n">
         <v>0.04240724355073125</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.004845301923607056</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.004943643732515851</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.020296322181629</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.02029632218162889</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -603,6 +683,18 @@
       <c r="F7" t="n">
         <v>0.0733193518890555</v>
       </c>
+      <c r="G7" t="n">
+        <v>0.004735839539037447</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.004797534557857531</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.013027261230355</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01302726123035483</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -627,6 +719,18 @@
       <c r="F8" t="n">
         <v>0.3735492914199685</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.005228211697860671</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.005650764638298679</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.080821696759317</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.08082169675931687</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -651,6 +755,18 @@
       <c r="F9" t="n">
         <v>0.137879228356192</v>
       </c>
+      <c r="G9" t="n">
+        <v>0.004925441698897414</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.004960129853321613</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.007042648465815</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.007042648465814544</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -675,6 +791,18 @@
       <c r="F10" t="n">
         <v>0.08366742226612686</v>
       </c>
+      <c r="G10" t="n">
+        <v>0.005700602187542488</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.006026515009469422</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.057171648047841</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.05717164804784156</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -699,6 +827,18 @@
       <c r="F11" t="n">
         <v>0.03269762106683138</v>
       </c>
+      <c r="G11" t="n">
+        <v>0.003469464017681089</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.003485537729003947</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.004632909072105</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.004632909072105395</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -723,6 +863,18 @@
       <c r="F12" t="n">
         <v>0.3138693461246695</v>
       </c>
+      <c r="G12" t="n">
+        <v>0.002366038878105913</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.002432181183726548</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.027954868465045</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0279548684650455</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -747,6 +899,18 @@
       <c r="F13" t="n">
         <v>0.6944267669059984</v>
       </c>
+      <c r="G13" t="n">
+        <v>0.00515469845913397</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.005792367375742907</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.12370634706653</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1237063470665306</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -771,6 +935,18 @@
       <c r="F14" t="n">
         <v>0.1535610435427738</v>
       </c>
+      <c r="G14" t="n">
+        <v>0.004806004653955109</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.004825515500299084</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.004059681117437</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.004059681117436875</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -795,6 +971,18 @@
       <c r="F15" t="n">
         <v>0.04932705564172996</v>
       </c>
+      <c r="G15" t="n">
+        <v>0.005647497574377197</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.005787664646778266</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.024819324055491</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0248193240554913</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -819,6 +1007,18 @@
       <c r="F16" t="n">
         <v>0.04820502046688305</v>
       </c>
+      <c r="G16" t="n">
+        <v>0.005263393168302922</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.005321842779490779</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.011104929713374</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.01110492971337415</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -843,6 +1043,18 @@
       <c r="F17" t="n">
         <v>0.1168459576615794</v>
       </c>
+      <c r="G17" t="n">
+        <v>0.006187150218696666</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.006551545079005293</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.058895428012638</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.058895428012638</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -867,6 +1079,18 @@
       <c r="F18" t="n">
         <v>0.01024810443712294</v>
       </c>
+      <c r="G18" t="n">
+        <v>0.005046983454967185</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.005075460180533234</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.005642325920055</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.005642325920054703</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -891,6 +1115,18 @@
       <c r="F19" t="n">
         <v>0.04462393759609339</v>
       </c>
+      <c r="G19" t="n">
+        <v>0.005062448047442335</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.005120310999371652</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.011429836195267</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.01142983619526722</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -915,6 +1151,18 @@
       <c r="F20" t="n">
         <v>0.01644471171724888</v>
       </c>
+      <c r="G20" t="n">
+        <v>0.004465605874459311</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.004486944506137899</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.004778440435291</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.004778440435290686</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -939,6 +1187,18 @@
       <c r="F21" t="n">
         <v>0.2577004177248663</v>
       </c>
+      <c r="G21" t="n">
+        <v>0.005311546050857084</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.005816451579070132</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.095058109894684</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0950581098946839</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -963,6 +1223,18 @@
       <c r="F22" t="n">
         <v>-0.02214985908554166</v>
       </c>
+      <c r="G22" t="n">
+        <v>0.005307010211890463</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.005301296132683509</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9989232959842151</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.001076704015784895</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -987,6 +1259,18 @@
       <c r="F23" t="n">
         <v>1.455823148129523</v>
       </c>
+      <c r="G23" t="n">
+        <v>0.005653476397055861</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.006223018997189907</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.100742014317181</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1007420143171811</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1011,6 +1295,18 @@
       <c r="F24" t="n">
         <v>1.281955606488145</v>
       </c>
+      <c r="G24" t="n">
+        <v>0.005369340637250635</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.006471316986997647</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.205234948608378</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2052349486083784</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1035,6 +1331,18 @@
       <c r="F25" t="n">
         <v>0.3000753497747035</v>
       </c>
+      <c r="G25" t="n">
+        <v>0.00492373003927194</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.005417656572151318</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.100315518710367</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1003155187103666</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1059,6 +1367,18 @@
       <c r="F26" t="n">
         <v>0.07143711050828809</v>
       </c>
+      <c r="G26" t="n">
+        <v>0.005559717396265502</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.00560628303292297</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.008375540218779</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.008375540218779223</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1083,6 +1403,18 @@
       <c r="F27" t="n">
         <v>0.06398529743381205</v>
       </c>
+      <c r="G27" t="n">
+        <v>0.004697123141272627</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.004979724367154967</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.060164747097895</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.06016474709789532</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1107,6 +1439,18 @@
       <c r="F28" t="n">
         <v>0.09637205803374047</v>
       </c>
+      <c r="G28" t="n">
+        <v>0.004415199218430886</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.004645406963538698</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.052139831912188</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.05213983191218838</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1131,6 +1475,18 @@
       <c r="F29" t="n">
         <v>1.093008279341058</v>
       </c>
+      <c r="G29" t="n">
+        <v>0.007281471987719291</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.007789876174208813</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.069821622241627</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.06982162224162659</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1155,6 +1511,18 @@
       <c r="F30" t="n">
         <v>0.1766947127960498</v>
       </c>
+      <c r="G30" t="n">
+        <v>0.005987368122010789</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0063119964909382</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.054218875858661</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.05421887585866159</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1179,6 +1547,18 @@
       <c r="F31" t="n">
         <v>0.2685003406070069</v>
       </c>
+      <c r="G31" t="n">
+        <v>0.005239931681158785</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.005491939420349041</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.048093707041334</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.04809370704133398</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1203,6 +1583,18 @@
       <c r="F32" t="n">
         <v>0.54951991735463</v>
       </c>
+      <c r="G32" t="n">
+        <v>0.004686089665955752</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.005090957658365871</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.086397833005943</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.08639783300594275</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1227,6 +1619,18 @@
       <c r="F33" t="n">
         <v>0.04967732834522437</v>
       </c>
+      <c r="G33" t="n">
+        <v>0.004253576863289791</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.004470141421399901</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.050913517040013</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.05091351704001305</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1251,6 +1655,18 @@
       <c r="F34" t="n">
         <v>-0.01227618004270912</v>
       </c>
+      <c r="G34" t="n">
+        <v>0.004553548190668175</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.004571702060604105</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.003986752566522</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.003986752566522559</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1275,6 +1691,18 @@
       <c r="F35" t="n">
         <v>0.4315962447688881</v>
       </c>
+      <c r="G35" t="n">
+        <v>0.0051728762363953</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.005460016141436381</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.055508752175593</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.05550875217559297</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1299,6 +1727,18 @@
       <c r="F36" t="n">
         <v>0.006738710048723228</v>
       </c>
+      <c r="G36" t="n">
+        <v>0.005336278021127436</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.005362550699334724</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.004923408807275</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.004923408807275056</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1323,6 +1763,18 @@
       <c r="F37" t="n">
         <v>0.002319105325786189</v>
       </c>
+      <c r="G37" t="n">
+        <v>0.004842631172563612</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.004866212890167441</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.004869608434653</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.004869608434653061</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1347,6 +1799,18 @@
       <c r="F38" t="n">
         <v>0.05211296842709761</v>
       </c>
+      <c r="G38" t="n">
+        <v>0.004009015308672882</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.004044238039613751</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.008785880878197</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.008785880878197257</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1371,6 +1835,18 @@
       <c r="F39" t="n">
         <v>0.005796949128526989</v>
       </c>
+      <c r="G39" t="n">
+        <v>0.005452548113302701</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.005478193059645763</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.004703295745432</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.004703295745432406</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1395,6 +1871,18 @@
       <c r="F40" t="n">
         <v>0.2638804377596934</v>
       </c>
+      <c r="G40" t="n">
+        <v>0.004314420264758406</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.004345897539924402</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.007295829621215</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.007295829621215144</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1419,6 +1907,18 @@
       <c r="F41" t="n">
         <v>0.5734612831675754</v>
       </c>
+      <c r="G41" t="n">
+        <v>0.004864375109071319</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.005153334958549616</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.05940328264147</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.05940328264147036</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1443,6 +1943,18 @@
       <c r="F42" t="n">
         <v>0.01543139833722677</v>
       </c>
+      <c r="G42" t="n">
+        <v>0.002535490177408771</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.002565289807663753</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.011753005600454</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.01175300560045439</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1467,6 +1979,18 @@
       <c r="F43" t="n">
         <v>0.07512265517921285</v>
       </c>
+      <c r="G43" t="n">
+        <v>0.005622217497283565</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.005753655799961237</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.023378373878488</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.02337837387848799</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1491,6 +2015,18 @@
       <c r="F44" t="n">
         <v>0.1440541756475316</v>
       </c>
+      <c r="G44" t="n">
+        <v>0.005643041871986667</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.005783235786438458</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.024843677865966</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.02484367786596546</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1515,6 +2051,18 @@
       <c r="F45" t="n">
         <v>0.05426119583502605</v>
       </c>
+      <c r="G45" t="n">
+        <v>0.005898294432716725</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.006154218122670837</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.0433894395869</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.04338943958690018</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1539,6 +2087,18 @@
       <c r="F46" t="n">
         <v>0.02838778185700768</v>
       </c>
+      <c r="G46" t="n">
+        <v>0.005422498675527013</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.005542147073476832</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.022065177902176</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.0220651779021763</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1563,6 +2123,18 @@
       <c r="F47" t="n">
         <v>0.2594668369643083</v>
       </c>
+      <c r="G47" t="n">
+        <v>0.005334060285385279</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.005869117280950887</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.100309514129715</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.1003095141297152</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1587,6 +2159,18 @@
       <c r="F48" t="n">
         <v>0.08982438650423188</v>
       </c>
+      <c r="G48" t="n">
+        <v>0.005153981931799554</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.005407703044291736</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.049228172673006</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.04922817267300618</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1611,6 +2195,18 @@
       <c r="F49" t="n">
         <v>0.03441472327405207</v>
       </c>
+      <c r="G49" t="n">
+        <v>0.004022461547233162</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.004078356647008754</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.013895744960953</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.01389574496095282</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1635,6 +2231,18 @@
       <c r="F50" t="n">
         <v>0.1450504444920725</v>
       </c>
+      <c r="G50" t="n">
+        <v>0.005266608492948535</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.005623884789267401</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.067838020767487</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.06783802076748686</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1659,6 +2267,18 @@
       <c r="F51" t="n">
         <v>0.01417369098481311</v>
       </c>
+      <c r="G51" t="n">
+        <v>0.005791925688145094</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.005822522227761574</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.005282619505824</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.005282619505824264</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1683,6 +2303,18 @@
       <c r="F52" t="n">
         <v>0.5293307659313218</v>
       </c>
+      <c r="G52" t="n">
+        <v>0.005060297753760877</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.005849967308793062</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.156051994064043</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.1560519940640435</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1707,6 +2339,18 @@
       <c r="F53" t="n">
         <v>1.350112188154365</v>
       </c>
+      <c r="G53" t="n">
+        <v>0.004383243506370678</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.004536942027045409</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.035065019876569</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.03506501987656918</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1731,6 +2375,18 @@
       <c r="F54" t="n">
         <v>0.02315105678491804</v>
       </c>
+      <c r="G54" t="n">
+        <v>0.003962462380882554</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.003982989911592964</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.005180498573172</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.005180498573172237</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1755,6 +2411,18 @@
       <c r="F55" t="n">
         <v>0.1006290949029046</v>
       </c>
+      <c r="G55" t="n">
+        <v>0.00490828352978066</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.004958610591222063</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.010253495165071</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.01025349516507095</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1779,6 +2447,18 @@
       <c r="F56" t="n">
         <v>0.2040850073090391</v>
       </c>
+      <c r="G56" t="n">
+        <v>0.005429984405781685</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.006130710184450541</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.129047475333952</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.129047475333952</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1803,6 +2483,18 @@
       <c r="F57" t="n">
         <v>0.0578529136708507</v>
       </c>
+      <c r="G57" t="n">
+        <v>0.00392302414616869</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.003959496021457273</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.009296877594853</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.009296877594853131</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1827,6 +2519,18 @@
       <c r="F58" t="n">
         <v>0.2471308212870846</v>
       </c>
+      <c r="G58" t="n">
+        <v>0.005489457327215333</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.005713688581817</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.040847617758132</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.04084761775813152</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1851,6 +2555,18 @@
       <c r="F59" t="n">
         <v>0.2771718364553214</v>
       </c>
+      <c r="G59" t="n">
+        <v>0.005638064812983782</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.005710973742284939</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.012931552176069</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.01293155217606871</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1875,6 +2591,18 @@
       <c r="F60" t="n">
         <v>0.143279506352133</v>
       </c>
+      <c r="G60" t="n">
+        <v>0.005390629197070221</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.005710345761462531</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.059309693303719</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.05930969330371925</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1899,6 +2627,18 @@
       <c r="F61" t="n">
         <v>-0.06597773515147944</v>
       </c>
+      <c r="G61" t="n">
+        <v>0.006011275375102831</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.006013112418950987</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.00030559968285</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.0003055996828501267</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1923,6 +2663,18 @@
       <c r="F62" t="n">
         <v>0.03596348288581505</v>
       </c>
+      <c r="G62" t="n">
+        <v>0.005493970945443856</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.005591519146149977</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.017755499924334</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.01775549992433394</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1947,6 +2699,18 @@
       <c r="F63" t="n">
         <v>0.02150128797620595</v>
       </c>
+      <c r="G63" t="n">
+        <v>0.005068534748521255</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.00509211658891186</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.004652595189859</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.004652595189859387</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1971,6 +2735,18 @@
       <c r="F64" t="n">
         <v>0.3005114737697626</v>
       </c>
+      <c r="G64" t="n">
+        <v>0.005615191834422185</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.005937287719333501</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.057361510418363</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.05736151041836313</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1995,6 +2771,18 @@
       <c r="F65" t="n">
         <v>0.6504577190636479</v>
       </c>
+      <c r="G65" t="n">
+        <v>0.004784440345779533</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.005088194638959754</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.063487946599265</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.06348794659926528</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2019,6 +2807,18 @@
       <c r="F66" t="n">
         <v>0.03811669170916488</v>
       </c>
+      <c r="G66" t="n">
+        <v>0.005504051669898882</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.005526251624008584</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.004033384030733</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.00403338403073337</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2043,6 +2843,18 @@
       <c r="F67" t="n">
         <v>0.2741034307255756</v>
       </c>
+      <c r="G67" t="n">
+        <v>0.003575027984592325</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.003938619868825353</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.101703227443264</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.1017032274432643</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2067,6 +2879,18 @@
       <c r="F68" t="n">
         <v>0.1095685811765028</v>
       </c>
+      <c r="G68" t="n">
+        <v>0.006414894348209245</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.006820889640498902</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.06328947450288</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.06328947450287985</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2091,6 +2915,18 @@
       <c r="F69" t="n">
         <v>0.004862658581264319</v>
       </c>
+      <c r="G69" t="n">
+        <v>0.004633740461632506</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.004655064020020797</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.004601802488692</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.004601802488691618</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2115,6 +2951,18 @@
       <c r="F70" t="n">
         <v>0.162435401222668</v>
       </c>
+      <c r="G70" t="n">
+        <v>0.005761257770470984</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.006035728637507907</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.047640789211639</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.04764078921163856</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2139,6 +2987,18 @@
       <c r="F71" t="n">
         <v>0.04435559409555734</v>
       </c>
+      <c r="G71" t="n">
+        <v>0.004454278024505289</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.004491218992385733</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.008293368235484</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.008293368235483477</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2163,6 +3023,18 @@
       <c r="F72" t="n">
         <v>-0.3140605214162253</v>
       </c>
+      <c r="G72" t="n">
+        <v>0.005267639038142327</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.005334229735779036</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.012641469385912</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.01264146938591157</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2187,6 +3059,18 @@
       <c r="F73" t="n">
         <v>0.4765274815220479</v>
       </c>
+      <c r="G73" t="n">
+        <v>0.005628574411131764</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.006288475729303606</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.117241288818487</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1172412888184866</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2211,6 +3095,18 @@
       <c r="F74" t="n">
         <v>0.1264027557750601</v>
       </c>
+      <c r="G74" t="n">
+        <v>0.005784692601684993</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.006050370324069724</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.045927716592467</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.04592771659246732</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2235,6 +3131,18 @@
       <c r="F75" t="n">
         <v>0.3628489322566342</v>
       </c>
+      <c r="G75" t="n">
+        <v>0.005325907285843794</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.005652114255494869</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.061249089055329</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.06124908905532946</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2259,6 +3167,18 @@
       <c r="F76" t="n">
         <v>-0.0387876619368059</v>
       </c>
+      <c r="G76" t="n">
+        <v>0.004480808419653054</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.004474788329055015</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.9986564722179073</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-0.001343527782092626</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2283,6 +3203,18 @@
       <c r="F77" t="n">
         <v>0.04985412374200178</v>
       </c>
+      <c r="G77" t="n">
+        <v>0.003627074684387098</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.003657900534899022</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.008498818798691</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.008498818798690605</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2307,6 +3239,18 @@
       <c r="F78" t="n">
         <v>0.1288848144001424</v>
       </c>
+      <c r="G78" t="n">
+        <v>0.003879792076407563</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.003943788046638683</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.016494690687233</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.01649469068723286</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2331,6 +3275,18 @@
       <c r="F79" t="n">
         <v>0.09947953646509454</v>
       </c>
+      <c r="G79" t="n">
+        <v>0.003277791348291767</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.003305087480199269</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.00832759898574</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.008327598985739995</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2355,6 +3311,18 @@
       <c r="F80" t="n">
         <v>0.126258989428363</v>
       </c>
+      <c r="G80" t="n">
+        <v>0.004822743609870303</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.004859512266791478</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.007624012366306</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.007624012366306112</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2379,6 +3347,18 @@
       <c r="F81" t="n">
         <v>0.1154384446165042</v>
       </c>
+      <c r="G81" t="n">
+        <v>0.005505289153948207</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.005604747899112549</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.018066034750057</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.01806603475005746</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2403,6 +3383,18 @@
       <c r="F82" t="n">
         <v>0.01856665783003959</v>
       </c>
+      <c r="G82" t="n">
+        <v>0.004452046716725676</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.004477146027893911</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.005637701660663</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.005637701660663328</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2427,6 +3419,18 @@
       <c r="F83" t="n">
         <v>0.03651737747586119</v>
       </c>
+      <c r="G83" t="n">
+        <v>0.005265361971736496</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.005477375514307378</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1.040265710830315</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.0402657108303154</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2451,6 +3455,18 @@
       <c r="F84" t="n">
         <v>0.2174052931256826</v>
       </c>
+      <c r="G84" t="n">
+        <v>0.0038604604810721</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.004265032692235346</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1.1047989516139</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.1047989516138995</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2475,6 +3491,18 @@
       <c r="F85" t="n">
         <v>-0.0001770805515797883</v>
       </c>
+      <c r="G85" t="n">
+        <v>0.006327972447624566</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.006810436719995931</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.076243105728514</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.0762431057285143</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2499,6 +3527,18 @@
       <c r="F86" t="n">
         <v>-8.47651746268236e-05</v>
       </c>
+      <c r="G86" t="n">
+        <v>0.00633329584081989</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.006818486261830371</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.076609467361889</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.07660946736188931</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2523,6 +3563,18 @@
       <c r="F87" t="n">
         <v>0.07771850084479608</v>
       </c>
+      <c r="G87" t="n">
+        <v>0.005401911025917049</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.005445324469943222</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.008036682540287</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.008036682540287379</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2547,6 +3599,18 @@
       <c r="F88" t="n">
         <v>0.1213881021662239</v>
       </c>
+      <c r="G88" t="n">
+        <v>0.005252263517998434</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.005535196831689114</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1.053868834402753</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.05386883440275331</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2571,6 +3635,18 @@
       <c r="F89" t="n">
         <v>0.03984264953985698</v>
       </c>
+      <c r="G89" t="n">
+        <v>0.00527534951939903</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.005367011119916932</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.017375455442494</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.01737545544249433</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2595,6 +3671,18 @@
       <c r="F90" t="n">
         <v>0.2040528031579761</v>
       </c>
+      <c r="G90" t="n">
+        <v>0.003865202894929595</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.003893772660482941</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1.007391530620766</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.007391530620766124</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2619,6 +3707,18 @@
       <c r="F91" t="n">
         <v>0.3966886654185131</v>
       </c>
+      <c r="G91" t="n">
+        <v>0.006130837502207331</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.006657132381127129</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1.085843880013181</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.08584388001318129</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2643,6 +3743,18 @@
       <c r="F92" t="n">
         <v>0.4654923071215157</v>
       </c>
+      <c r="G92" t="n">
+        <v>0.004440659002506743</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.005059882922721247</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1.139444150038306</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.1394441500383061</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2667,6 +3779,18 @@
       <c r="F93" t="n">
         <v>0.04921811966106003</v>
       </c>
+      <c r="G93" t="n">
+        <v>0.004184451267676556</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.004234059394791286</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1.011855348274202</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.01185534827420156</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2691,6 +3815,18 @@
       <c r="F94" t="n">
         <v>0.04689283361331522</v>
       </c>
+      <c r="G94" t="n">
+        <v>0.005020453009521485</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.005238163345219459</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1.043364679499057</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.04336467949905674</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2715,6 +3851,18 @@
       <c r="F95" t="n">
         <v>0.03885645638598939</v>
       </c>
+      <c r="G95" t="n">
+        <v>0.003699996954852592</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.003737794729427438</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1.010215623157547</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.01021562315754716</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2739,6 +3887,18 @@
       <c r="F96" t="n">
         <v>0.03888911850073115</v>
       </c>
+      <c r="G96" t="n">
+        <v>0.004980411019816891</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.005152410085066135</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1.034535114584894</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.03453511458489384</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2763,6 +3923,18 @@
       <c r="F97" t="n">
         <v>1.870539381002942</v>
       </c>
+      <c r="G97" t="n">
+        <v>0.003881242579063649</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.005637018634976428</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1.452374727975998</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.4523747279759979</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2787,6 +3959,18 @@
       <c r="F98" t="n">
         <v>0.09954844554465202</v>
       </c>
+      <c r="G98" t="n">
+        <v>0.004615136348621382</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.004635079367644429</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1.004321219898304</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.004321219898303553</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2811,6 +3995,18 @@
       <c r="F99" t="n">
         <v>0.06108504705632495</v>
       </c>
+      <c r="G99" t="n">
+        <v>0.005660589928945919</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.005714027998444989</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1.009440371086732</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.009440371086732452</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2835,6 +4031,18 @@
       <c r="F100" t="n">
         <v>0.260223915855335</v>
       </c>
+      <c r="G100" t="n">
+        <v>0.004613394526042138</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.004840492113408656</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1.04922570269778</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.04922570269778028</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2859,6 +4067,18 @@
       <c r="F101" t="n">
         <v>0.07088786674096924</v>
       </c>
+      <c r="G101" t="n">
+        <v>0.006036203022145263</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.00609921535766634</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1.010439068283473</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.01043906828347249</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2883,6 +4103,18 @@
       <c r="F102" t="n">
         <v>1.932676995623078</v>
       </c>
+      <c r="G102" t="n">
+        <v>0.004526247486457069</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.005735616199925827</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1.267190143068247</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.2671901430682472</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2907,6 +4139,18 @@
       <c r="F103" t="n">
         <v>0.09873596171429025</v>
       </c>
+      <c r="G103" t="n">
+        <v>0.004786501328281187</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.004827972110464603</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1.008664111704803</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.008664111704803008</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2931,6 +4175,18 @@
       <c r="F104" t="n">
         <v>-0.01708782819794662</v>
       </c>
+      <c r="G104" t="n">
+        <v>0.006998228090665987</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.007012594659001582</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1.002052886552063</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.002052886552062576</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2955,6 +4211,18 @@
       <c r="F105" t="n">
         <v>-0.01696075166485171</v>
       </c>
+      <c r="G105" t="n">
+        <v>0.007390239422842248</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.007402150824727684</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1.001611774829462</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.001611774829462181</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2979,6 +4247,18 @@
       <c r="F106" t="n">
         <v>3.574056075809853</v>
       </c>
+      <c r="G106" t="n">
+        <v>0.006443920602358332</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.007314702207326743</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.135132267869614</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.135132267869614</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3003,6 +4283,18 @@
       <c r="F107" t="n">
         <v>0.7368914635216627</v>
       </c>
+      <c r="G107" t="n">
+        <v>0.003982499667036932</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.004396837541097011</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1.10403965064694</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.1040396506469403</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3027,6 +4319,18 @@
       <c r="F108" t="n">
         <v>0.509248248837691</v>
       </c>
+      <c r="G108" t="n">
+        <v>0.005083082264454132</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.005700564771295315</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1.12147796842857</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.1214779684285699</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3051,6 +4355,18 @@
       <c r="F109" t="n">
         <v>-0.1652568518656434</v>
       </c>
+      <c r="G109" t="n">
+        <v>0.005978253014460307</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.005974869322068286</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.9994339998016416</v>
+      </c>
+      <c r="J109" t="n">
+        <v>-0.0005660001983584195</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3075,6 +4391,18 @@
       <c r="F110" t="n">
         <v>0.0668495493578303</v>
       </c>
+      <c r="G110" t="n">
+        <v>0.004083185355749554</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.004260764289643881</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1.043490294567274</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.04349029456727379</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3099,6 +4427,18 @@
       <c r="F111" t="n">
         <v>0.2181503544674689</v>
       </c>
+      <c r="G111" t="n">
+        <v>0.006025158633442575</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.006251302208516758</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1.037533215112209</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.03753321511220886</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3123,6 +4463,18 @@
       <c r="F112" t="n">
         <v>0.1388723787046827</v>
       </c>
+      <c r="G112" t="n">
+        <v>0.005196341526207598</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.005746726696122873</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1.105917820670451</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.1059178206704512</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3147,6 +4499,18 @@
       <c r="F113" t="n">
         <v>0.8891525801407416</v>
       </c>
+      <c r="G113" t="n">
+        <v>0.00301553911124778</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.003471345982248138</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1.151152697472974</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.1511526974729744</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3171,6 +4535,18 @@
       <c r="F114" t="n">
         <v>0.08647722590557244</v>
       </c>
+      <c r="G114" t="n">
+        <v>0.003056796403788469</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.003096460258545793</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.012975628572504</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.01297562857250379</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3195,6 +4571,18 @@
       <c r="F115" t="n">
         <v>0.01412214897563901</v>
       </c>
+      <c r="G115" t="n">
+        <v>0.005426336819289736</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.005464943462776204</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.007114678792003</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.007114678792003293</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3219,6 +4607,18 @@
       <c r="F116" t="n">
         <v>0.06492988910730331</v>
       </c>
+      <c r="G116" t="n">
+        <v>0.004794306309338327</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.00503211644263874</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.049602615677102</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.04960261567710172</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3243,6 +4643,18 @@
       <c r="F117" t="n">
         <v>0.3762396511352327</v>
       </c>
+      <c r="G117" t="n">
+        <v>0.005003720161355483</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.005219054819048529</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.043034912175167</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.0430349121751669</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3267,6 +4679,18 @@
       <c r="F118" t="n">
         <v>0.01812471095672286</v>
       </c>
+      <c r="G118" t="n">
+        <v>0.00423567557785494</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.004256764392330379</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1.004978854987312</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.004978854987312114</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3291,6 +4715,18 @@
       <c r="F119" t="n">
         <v>0.4982214376805831</v>
       </c>
+      <c r="G119" t="n">
+        <v>0.005513701372992923</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.00597321021053751</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.083339449574716</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.08333944957471609</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3315,6 +4751,18 @@
       <c r="F120" t="n">
         <v>0.03989363729394624</v>
       </c>
+      <c r="G120" t="n">
+        <v>0.003501106401807212</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.003534934481552504</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1.009662111305109</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.009662111305109307</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3339,6 +4787,18 @@
       <c r="F121" t="n">
         <v>0.1730256856053433</v>
       </c>
+      <c r="G121" t="n">
+        <v>0.005782933977513421</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.00589524956396882</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1.019421903637865</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.0194219036378648</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3363,6 +4823,18 @@
       <c r="F122" t="n">
         <v>0.02515413650253518</v>
       </c>
+      <c r="G122" t="n">
+        <v>0.003526917471503535</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.003555762015688614</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1.008178400662373</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.008178400662372893</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3387,6 +4859,18 @@
       <c r="F123" t="n">
         <v>0.01662418044942931</v>
       </c>
+      <c r="G123" t="n">
+        <v>0.005195894680527963</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.005330248174722919</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1.025857624616306</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.02585762461630653</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3411,6 +4895,18 @@
       <c r="F124" t="n">
         <v>0.05123176110880514</v>
       </c>
+      <c r="G124" t="n">
+        <v>0.004762216932184977</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.004982829998926474</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1.046325707098831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.04632570709883138</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3435,6 +4931,18 @@
       <c r="F125" t="n">
         <v>0.04731220969809899</v>
       </c>
+      <c r="G125" t="n">
+        <v>0.004415000691865205</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.004605968368597829</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1.043254280137371</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.04325428013737096</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3459,6 +4967,18 @@
       <c r="F126" t="n">
         <v>0.05683787790752594</v>
       </c>
+      <c r="G126" t="n">
+        <v>0.00530135459906003</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.005562249772595093</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.049212926368163</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.04921292636816285</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3483,6 +5003,18 @@
       <c r="F127" t="n">
         <v>0.5193761745695844</v>
       </c>
+      <c r="G127" t="n">
+        <v>0.005383037982814084</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.005687743554034476</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.056604759653043</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.05660475965304287</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3507,6 +5039,18 @@
       <c r="F128" t="n">
         <v>0.2577502726542619</v>
       </c>
+      <c r="G128" t="n">
+        <v>0.005597835842870543</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.005821101843913524</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1.039884342326211</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.03988434232621063</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3531,6 +5075,18 @@
       <c r="F129" t="n">
         <v>0.1070815732378713</v>
       </c>
+      <c r="G129" t="n">
+        <v>0.005819985773141492</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.006088933954221189</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1.046211140639013</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.04621114063901312</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3555,6 +5111,18 @@
       <c r="F130" t="n">
         <v>0.09048886820062371</v>
       </c>
+      <c r="G130" t="n">
+        <v>0.00509131869058463</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.005245092703312334</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1.030203179583332</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.03020317958333234</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3579,6 +5147,18 @@
       <c r="F131" t="n">
         <v>0.2583857692711665</v>
       </c>
+      <c r="G131" t="n">
+        <v>0.005279686227743294</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.005644099500516854</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1.069021767024462</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.0690217670244623</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3603,6 +5183,18 @@
       <c r="F132" t="n">
         <v>0.1019798671587204</v>
       </c>
+      <c r="G132" t="n">
+        <v>0.004689172382579182</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.004844368958896282</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1.033096794840316</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.03309679484031617</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3627,6 +5219,18 @@
       <c r="F133" t="n">
         <v>0.05421897242180251</v>
       </c>
+      <c r="G133" t="n">
+        <v>0.002647575847410403</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.0026706293279801</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1.008707391930715</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.008707391930714806</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3651,6 +5255,18 @@
       <c r="F134" t="n">
         <v>0.1535913350131898</v>
       </c>
+      <c r="G134" t="n">
+        <v>0.005412146838155584</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.00568850396548282</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.051062385332733</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.05106238533273341</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3675,6 +5291,18 @@
       <c r="F135" t="n">
         <v>0.4833566499589356</v>
       </c>
+      <c r="G135" t="n">
+        <v>0.004628667338778467</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.005167054596188424</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.116315824405744</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.1163158244057436</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3699,6 +5327,18 @@
       <c r="F136" t="n">
         <v>0.06570699938692352</v>
       </c>
+      <c r="G136" t="n">
+        <v>0.003700747466316331</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.003739299627922853</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1.010417398635659</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.01041739863565889</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3723,6 +5363,18 @@
       <c r="F137" t="n">
         <v>0.01293565265629442</v>
       </c>
+      <c r="G137" t="n">
+        <v>0.004774979206932107</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.004803417515029711</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.005955692551775</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.005955692551774447</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3747,6 +5399,18 @@
       <c r="F138" t="n">
         <v>0.03088872086782701</v>
       </c>
+      <c r="G138" t="n">
+        <v>0.00259397363525905</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.002633795226438657</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.015351578997691</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.01535157899769125</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3771,6 +5435,18 @@
       <c r="F139" t="n">
         <v>-0.08570972646654157</v>
       </c>
+      <c r="G139" t="n">
+        <v>0.006668235600639313</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.00689566095462664</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1.034105776641354</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.03410577664135366</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3795,6 +5471,18 @@
       <c r="F140" t="n">
         <v>-0.08749076832819863</v>
       </c>
+      <c r="G140" t="n">
+        <v>0.006540654005125271</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.006756575659916905</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.033012242296021</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.03301224229602077</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3819,6 +5507,18 @@
       <c r="F141" t="n">
         <v>0.06889051038682403</v>
       </c>
+      <c r="G141" t="n">
+        <v>0.004213196546871988</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.004259521127963326</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1.010995115128377</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.01099511512837695</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3843,6 +5543,18 @@
       <c r="F142" t="n">
         <v>0.2173948608883115</v>
       </c>
+      <c r="G142" t="n">
+        <v>0.00399427819558875</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.004153520389036004</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1.039867576981273</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.03986757698127268</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3867,6 +5579,18 @@
       <c r="F143" t="n">
         <v>-0.005369171402924689</v>
       </c>
+      <c r="G143" t="n">
+        <v>0.006044237340389758</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.006094440843671425</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1.008306011239199</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.00830601123919952</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3891,6 +5615,18 @@
       <c r="F144" t="n">
         <v>0.03330351062901411</v>
       </c>
+      <c r="G144" t="n">
+        <v>0.005227983284813805</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.005261758948618986</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1.006460553135909</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.006460553135908607</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3915,6 +5651,18 @@
       <c r="F145" t="n">
         <v>-0.007032770368970845</v>
       </c>
+      <c r="G145" t="n">
+        <v>0.00594429432235138</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.006009513820682243</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1.010971781475495</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.01097178147549462</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3939,6 +5687,18 @@
       <c r="F146" t="n">
         <v>0.1757763952247861</v>
       </c>
+      <c r="G146" t="n">
+        <v>0.005762122141044855</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.00613923781475952</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1.065447358539727</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.06544735853972747</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3963,6 +5723,18 @@
       <c r="F147" t="n">
         <v>0.1149107259881311</v>
       </c>
+      <c r="G147" t="n">
+        <v>0.005336576853522842</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.005411601709553224</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1.014058610620562</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.01405861062056207</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3987,6 +5759,18 @@
       <c r="F148" t="n">
         <v>0.3536392224857131</v>
       </c>
+      <c r="G148" t="n">
+        <v>0.004966959499284061</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.005331049289702058</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1.073302347335523</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.07330234733552332</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4011,6 +5795,18 @@
       <c r="F149" t="n">
         <v>0.4703322351160021</v>
       </c>
+      <c r="G149" t="n">
+        <v>0.004901366783861468</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.005580339139560106</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1.138527146740836</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.1385271467408362</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4035,6 +5831,18 @@
       <c r="F150" t="n">
         <v>0.3666947766477328</v>
       </c>
+      <c r="G150" t="n">
+        <v>0.004966749767483236</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.005612309219199498</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1.129976238372762</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.1299762383727621</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4059,6 +5867,18 @@
       <c r="F151" t="n">
         <v>0.3566314967284746</v>
       </c>
+      <c r="G151" t="n">
+        <v>0.005657758967762709</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.006044447057044828</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1.068346511663969</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.06834651166396891</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4083,6 +5903,18 @@
       <c r="F152" t="n">
         <v>0.217138869232974</v>
       </c>
+      <c r="G152" t="n">
+        <v>0.005212525385645138</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.005445590774778008</v>
+      </c>
+      <c r="I152" t="n">
+        <v>1.044712566729116</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.044712566729116</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4107,6 +5939,18 @@
       <c r="F153" t="n">
         <v>0.1796494979400157</v>
       </c>
+      <c r="G153" t="n">
+        <v>0.004548886824146346</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.004720389638787017</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1.0377021502778</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.03770215027780031</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4131,6 +5975,18 @@
       <c r="F154" t="n">
         <v>0.3905084495294514</v>
       </c>
+      <c r="G154" t="n">
+        <v>0.005990885051816042</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.006381030838792414</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1.0651232303077</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.0651232303076999</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4155,6 +6011,18 @@
       <c r="F155" t="n">
         <v>0.06421302496970424</v>
       </c>
+      <c r="G155" t="n">
+        <v>0.005488393677888702</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.005565866979487985</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1.014115842657461</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.01411584265746137</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4179,6 +6047,18 @@
       <c r="F156" t="n">
         <v>0.07012084756333231</v>
       </c>
+      <c r="G156" t="n">
+        <v>0.004943233603334024</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.005175030589758116</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1.046891772678466</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.04689177267846571</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4203,6 +6083,18 @@
       <c r="F157" t="n">
         <v>0.2049597267110934</v>
       </c>
+      <c r="G157" t="n">
+        <v>0.00527118451514075</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.005572386625193593</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1.057141257185682</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.05714125718568203</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4227,6 +6119,18 @@
       <c r="F158" t="n">
         <v>0.08754589997206787</v>
       </c>
+      <c r="G158" t="n">
+        <v>0.005368291373593793</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.005391251124594347</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1.004276919675689</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.004276919675688802</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4251,6 +6155,18 @@
       <c r="F159" t="n">
         <v>0.01481910564311341</v>
       </c>
+      <c r="G159" t="n">
+        <v>0.004985760444695526</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.005010623932330628</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1.004986899774047</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.004986899774046562</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4275,6 +6191,18 @@
       <c r="F160" t="n">
         <v>0.01654155312835388</v>
       </c>
+      <c r="G160" t="n">
+        <v>0.006067591469033237</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.006137744744319659</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1.011561964190315</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.01156196419031483</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4299,6 +6227,18 @@
       <c r="F161" t="n">
         <v>0.03455015273382052</v>
       </c>
+      <c r="G161" t="n">
+        <v>0.005479770900658026</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.005518108412808613</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1.006996188863659</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.006996188863659116</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4323,6 +6263,18 @@
       <c r="F162" t="n">
         <v>0.3279098168330208</v>
       </c>
+      <c r="G162" t="n">
+        <v>0.004873631595158053</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.005283579404711025</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1.084115469449979</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.08411546944997955</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4347,6 +6299,18 @@
       <c r="F163" t="n">
         <v>2.830425869398122</v>
       </c>
+      <c r="G163" t="n">
+        <v>0.003921181401864682</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.005758570140979447</v>
+      </c>
+      <c r="I163" t="n">
+        <v>1.468580397285627</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.468580397285627</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4371,6 +6335,18 @@
       <c r="F164" t="n">
         <v>0.03880794538913635</v>
       </c>
+      <c r="G164" t="n">
+        <v>0.005740926144409885</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.005805110760378525</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1.011180184930813</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.01118018493081268</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4395,6 +6371,18 @@
       <c r="F165" t="n">
         <v>0.1406113326380818</v>
       </c>
+      <c r="G165" t="n">
+        <v>0.0041289385468056</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.004204341420137868</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1.018262047855036</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.01826204785503613</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4419,6 +6407,18 @@
       <c r="F166" t="n">
         <v>0.02101225045074403</v>
       </c>
+      <c r="G166" t="n">
+        <v>0.005877117029169873</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.00592446917184974</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1.008057035863816</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.008057035863816366</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4443,6 +6443,18 @@
       <c r="F167" t="n">
         <v>0.3418881868823385</v>
       </c>
+      <c r="G167" t="n">
+        <v>0.004844389777188411</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.004964429011624074</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1.02477902067272</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.02477902067271964</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4467,6 +6479,18 @@
       <c r="F168" t="n">
         <v>0.05373558469955702</v>
       </c>
+      <c r="G168" t="n">
+        <v>0.004700663691692694</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.004775350447004586</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1.015888555363764</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.01588855536376345</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4491,6 +6515,18 @@
       <c r="F169" t="n">
         <v>0.0996221811569661</v>
       </c>
+      <c r="G169" t="n">
+        <v>0.003894415118896421</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.003925205702224708</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1.007906343414416</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.007906343414415611</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4515,6 +6551,18 @@
       <c r="F170" t="n">
         <v>0.06825268268583523</v>
       </c>
+      <c r="G170" t="n">
+        <v>0.005747387967909815</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.005866558377440387</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1.020734707696079</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0.02073470769607906</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4539,6 +6587,18 @@
       <c r="F171" t="n">
         <v>0.1831212052319796</v>
       </c>
+      <c r="G171" t="n">
+        <v>0.005449796758089644</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0059653821773964</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1.094606357299733</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.09460635729973307</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4563,6 +6623,18 @@
       <c r="F172" t="n">
         <v>1.334825471831277</v>
       </c>
+      <c r="G172" t="n">
+        <v>0.004162464187554672</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.005590423081199575</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1.343056139176969</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0.3430561391769688</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4587,6 +6659,18 @@
       <c r="F173" t="n">
         <v>0.03665796896283693</v>
       </c>
+      <c r="G173" t="n">
+        <v>0.003980006891171064</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.003999736329042759</v>
+      </c>
+      <c r="I173" t="n">
+        <v>1.004957136610859</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0.004957136610858971</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4611,6 +6695,18 @@
       <c r="F174" t="n">
         <v>0.1220638163553421</v>
       </c>
+      <c r="G174" t="n">
+        <v>0.00621326255571527</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.006589409781166915</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1.060539406162008</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0.06053940616200832</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4635,6 +6731,18 @@
       <c r="F175" t="n">
         <v>0.135559600789265</v>
       </c>
+      <c r="G175" t="n">
+        <v>0.005671617884229583</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.005839190760083539</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1.029545868440803</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0.02954586844080353</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4659,6 +6767,18 @@
       <c r="F176" t="n">
         <v>0.1968578043484053</v>
       </c>
+      <c r="G176" t="n">
+        <v>0.005161045273196322</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.005170068998126828</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1.001748429717788</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0.001748429717788002</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4683,6 +6803,18 @@
       <c r="F177" t="n">
         <v>0.05455704884282726</v>
       </c>
+      <c r="G177" t="n">
+        <v>0.005472886504215735</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.0055939825146129</v>
+      </c>
+      <c r="I177" t="n">
+        <v>1.022126534197975</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0.02212653419797497</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4707,6 +6839,18 @@
       <c r="F178" t="n">
         <v>0.04952089289651181</v>
       </c>
+      <c r="G178" t="n">
+        <v>0.004347420651393393</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.004431172582183899</v>
+      </c>
+      <c r="I178" t="n">
+        <v>1.019264740522328</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0.01926474052232835</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4731,6 +6875,18 @@
       <c r="F179" t="n">
         <v>0.01227087311167518</v>
       </c>
+      <c r="G179" t="n">
+        <v>0.005078000568890852</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.005102835211071846</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1.004890633989515</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0.004890633989514933</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4755,6 +6911,18 @@
       <c r="F180" t="n">
         <v>0.1202696050770963</v>
       </c>
+      <c r="G180" t="n">
+        <v>0.004277860671285011</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.004474502495213309</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1.045967327839415</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0.04596732783941499</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4779,6 +6947,18 @@
       <c r="F181" t="n">
         <v>0.0939492336397014</v>
       </c>
+      <c r="G181" t="n">
+        <v>0.0035151376935886</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.003555378015081413</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1.011447722678463</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0.01144772267846269</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4803,6 +6983,18 @@
       <c r="F182" t="n">
         <v>0.374515148634317</v>
       </c>
+      <c r="G182" t="n">
+        <v>0.004765243351466467</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.004861907781046872</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1.020285308105127</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0.02028530810512692</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4827,6 +7019,18 @@
       <c r="F183" t="n">
         <v>0.04960936150898067</v>
       </c>
+      <c r="G183" t="n">
+        <v>0.003247219880431243</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.003277520760485448</v>
+      </c>
+      <c r="I183" t="n">
+        <v>1.009331329928352</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0.009331329928351414</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4851,6 +7055,18 @@
       <c r="F184" t="n">
         <v>0.01094101094586344</v>
       </c>
+      <c r="G184" t="n">
+        <v>0.00493842361911646</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.004965662987078902</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1.005515802220166</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0.00551580222016581</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4875,6 +7091,18 @@
       <c r="F185" t="n">
         <v>0.04755722358108763</v>
       </c>
+      <c r="G185" t="n">
+        <v>0.00332688872969455</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.003374004345075537</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1.014162065283534</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0.01416206528353378</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4899,6 +7127,18 @@
       <c r="F186" t="n">
         <v>0.06129233561811699</v>
       </c>
+      <c r="G186" t="n">
+        <v>0.004622578705284835</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.004832282559931842</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1.045365123671612</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0.04536512367161211</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4923,6 +7163,18 @@
       <c r="F187" t="n">
         <v>0.07563156988970682</v>
       </c>
+      <c r="G187" t="n">
+        <v>0.003793936831900681</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.003861712888428563</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1.017864308113408</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0.01786430811340834</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4947,6 +7199,18 @@
       <c r="F188" t="n">
         <v>0.04187565852650492</v>
       </c>
+      <c r="G188" t="n">
+        <v>0.003787020476174951</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.003827518545399651</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1.010693913455045</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.01069391345504527</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4971,6 +7235,18 @@
       <c r="F189" t="n">
         <v>0.1046597792463246</v>
       </c>
+      <c r="G189" t="n">
+        <v>0.005493353740822523</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.005918793995994689</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1.077446360683203</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0.07744636068320353</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4995,6 +7271,18 @@
       <c r="F190" t="n">
         <v>0.08288358773099952</v>
       </c>
+      <c r="G190" t="n">
+        <v>0.004782606251090559</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.005055587338784063</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1.057077892965004</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.05707789296500354</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5019,6 +7307,18 @@
       <c r="F191" t="n">
         <v>0.03511261944465965</v>
       </c>
+      <c r="G191" t="n">
+        <v>0.003921211105092393</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.003960313690396232</v>
+      </c>
+      <c r="I191" t="n">
+        <v>1.009972068388018</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0.009972068388018373</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5043,6 +7343,18 @@
       <c r="F192" t="n">
         <v>0.25427889829026</v>
       </c>
+      <c r="G192" t="n">
+        <v>0.006137598642256468</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.00630979678082535</v>
+      </c>
+      <c r="I192" t="n">
+        <v>1.028056272266375</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0.0280562722663752</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5067,6 +7379,18 @@
       <c r="F193" t="n">
         <v>0.4831589952018818</v>
       </c>
+      <c r="G193" t="n">
+        <v>0.005770582884037785</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.006475355319937647</v>
+      </c>
+      <c r="I193" t="n">
+        <v>1.122131931914427</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0.1221319319144272</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5091,6 +7415,18 @@
       <c r="F194" t="n">
         <v>0.02165693922964898</v>
       </c>
+      <c r="G194" t="n">
+        <v>0.004823824772434167</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.004847558787075807</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1.004920165172099</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0.004920165172099119</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5115,6 +7451,18 @@
       <c r="F195" t="n">
         <v>0.06484055477875802</v>
       </c>
+      <c r="G195" t="n">
+        <v>0.00616974144240913</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.006340990241801453</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1.027756235976958</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0.02775623597695765</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5139,6 +7487,18 @@
       <c r="F196" t="n">
         <v>0.125848677856274</v>
       </c>
+      <c r="G196" t="n">
+        <v>0.003954130484214044</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.004125079294388246</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1.043232971409688</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0.04323297140968806</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5163,6 +7523,18 @@
       <c r="F197" t="n">
         <v>0.1286725368612132</v>
       </c>
+      <c r="G197" t="n">
+        <v>0.004418541806568816</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.004458623014841804</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1.00907113930967</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0.009071139309670351</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5187,6 +7559,18 @@
       <c r="F198" t="n">
         <v>0.2316940358949787</v>
       </c>
+      <c r="G198" t="n">
+        <v>0.005701885697094238</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.006235116844919624</v>
+      </c>
+      <c r="I198" t="n">
+        <v>1.093518386048519</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0.09351838604851867</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5211,6 +7595,18 @@
       <c r="F199" t="n">
         <v>0.000328827466178768</v>
       </c>
+      <c r="G199" t="n">
+        <v>0.004585553455355855</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.004602503018194864</v>
+      </c>
+      <c r="I199" t="n">
+        <v>1.00369629598783</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.003696295987829465</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5235,6 +7631,18 @@
       <c r="F200" t="n">
         <v>0.1540632117923754</v>
       </c>
+      <c r="G200" t="n">
+        <v>0.00468926964447388</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.005014801899597575</v>
+      </c>
+      <c r="I200" t="n">
+        <v>1.069420673112138</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0.0694206731121384</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5259,6 +7667,18 @@
       <c r="F201" t="n">
         <v>0.04287682947813763</v>
       </c>
+      <c r="G201" t="n">
+        <v>0.004721104345872905</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.004757605476535787</v>
+      </c>
+      <c r="I201" t="n">
+        <v>1.007731481447723</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.007731481447723249</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5283,6 +7703,18 @@
       <c r="F202" t="n">
         <v>0.4500852078277731</v>
       </c>
+      <c r="G202" t="n">
+        <v>0.004095334341249084</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.00429762215045697</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1.049394699517058</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0.04939469951705778</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5307,6 +7739,18 @@
       <c r="F203" t="n">
         <v>0.01058368775660002</v>
       </c>
+      <c r="G203" t="n">
+        <v>0.004735704168633909</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.00475716942009083</v>
+      </c>
+      <c r="I203" t="n">
+        <v>1.004532641966762</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0.004532641966762129</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5331,6 +7775,18 @@
       <c r="F204" t="n">
         <v>0.06822280528601717</v>
       </c>
+      <c r="G204" t="n">
+        <v>0.005594919168748545</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.005911555638440742</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1.056593573587413</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0.05659357358741275</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5355,6 +7811,18 @@
       <c r="F205" t="n">
         <v>4.076464625051108</v>
       </c>
+      <c r="G205" t="n">
+        <v>0.006209023932602365</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.007151691423879511</v>
+      </c>
+      <c r="I205" t="n">
+        <v>1.151822170684088</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0.1518221706840884</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5379,6 +7847,18 @@
       <c r="F206" t="n">
         <v>3.474504344811322</v>
       </c>
+      <c r="G206" t="n">
+        <v>0.003503055597510714</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.00495373066541729</v>
+      </c>
+      <c r="I206" t="n">
+        <v>1.414117055103959</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0.4141170551039587</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5403,6 +7883,18 @@
       <c r="F207" t="n">
         <v>0.08534199083754462</v>
       </c>
+      <c r="G207" t="n">
+        <v>0.002912934806447916</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.002943371018743193</v>
+      </c>
+      <c r="I207" t="n">
+        <v>1.010448641771146</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0.01044864177114602</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5427,6 +7919,18 @@
       <c r="F208" t="n">
         <v>0.5980226388237513</v>
       </c>
+      <c r="G208" t="n">
+        <v>0.003345944967226473</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.003453667563250198</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1.032194969456721</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0.03219496945672078</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5451,6 +7955,18 @@
       <c r="F209" t="n">
         <v>0.5766404856704299</v>
       </c>
+      <c r="G209" t="n">
+        <v>0.003472892715719334</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.003567748370436596</v>
+      </c>
+      <c r="I209" t="n">
+        <v>1.027313154330371</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.02731315433037052</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5475,6 +7991,18 @@
       <c r="F210" t="n">
         <v>0.04431358838831271</v>
       </c>
+      <c r="G210" t="n">
+        <v>0.00465136524050766</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.0048390922137139</v>
+      </c>
+      <c r="I210" t="n">
+        <v>1.040359542521273</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0.04035954252127288</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5499,6 +8027,18 @@
       <c r="F211" t="n">
         <v>0.04114162461255406</v>
       </c>
+      <c r="G211" t="n">
+        <v>0.004323988899160104</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.004375932264248334</v>
+      </c>
+      <c r="I211" t="n">
+        <v>1.012012834977055</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0.01201283497705547</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5523,6 +8063,18 @@
       <c r="F212" t="n">
         <v>0.02995421796844702</v>
       </c>
+      <c r="G212" t="n">
+        <v>0.003002472238858838</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.003025206958344371</v>
+      </c>
+      <c r="I212" t="n">
+        <v>1.007571999897715</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0.007571999897715349</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5547,6 +8099,18 @@
       <c r="F213" t="n">
         <v>0.08732229673326734</v>
       </c>
+      <c r="G213" t="n">
+        <v>0.005753510774220174</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.006032681080523657</v>
+      </c>
+      <c r="I213" t="n">
+        <v>1.04852173173193</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0.0485217317319305</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5571,6 +8135,18 @@
       <c r="F214" t="n">
         <v>0.1034213461655405</v>
       </c>
+      <c r="G214" t="n">
+        <v>0.004992269959657262</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.005302818691994123</v>
+      </c>
+      <c r="I214" t="n">
+        <v>1.062205917317457</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0.06220591731745643</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5595,6 +8171,18 @@
       <c r="F215" t="n">
         <v>0.04519003689340517</v>
       </c>
+      <c r="G215" t="n">
+        <v>0.004692369813318748</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.00480162406716418</v>
+      </c>
+      <c r="I215" t="n">
+        <v>1.023283385195968</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0.02328338519596766</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5619,6 +8207,18 @@
       <c r="F216" t="n">
         <v>0.176989682981643</v>
       </c>
+      <c r="G216" t="n">
+        <v>0.005251954646821422</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.005621245972675986</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1.07031502567869</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0.0703150256786902</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5643,6 +8243,18 @@
       <c r="F217" t="n">
         <v>0.06786129789224754</v>
       </c>
+      <c r="G217" t="n">
+        <v>0.00540567473139178</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.005708624694178961</v>
+      </c>
+      <c r="I217" t="n">
+        <v>1.056042950758375</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0.0560429507583749</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5667,6 +8279,18 @@
       <c r="F218" t="n">
         <v>0.05197991783942323</v>
       </c>
+      <c r="G218" t="n">
+        <v>0.005123781404860327</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.005225039869678267</v>
+      </c>
+      <c r="I218" t="n">
+        <v>1.019762448242208</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0.01976244824220802</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5691,6 +8315,18 @@
       <c r="F219" t="n">
         <v>0.2576956057819024</v>
       </c>
+      <c r="G219" t="n">
+        <v>0.005528980771566605</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.005894843546023718</v>
+      </c>
+      <c r="I219" t="n">
+        <v>1.066171829777127</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0.06617182977712684</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5715,6 +8351,18 @@
       <c r="F220" t="n">
         <v>0.09667838275469706</v>
       </c>
+      <c r="G220" t="n">
+        <v>0.004811475889214075</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.004841818579097805</v>
+      </c>
+      <c r="I220" t="n">
+        <v>1.006306316519584</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0.006306316519583836</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5739,6 +8387,18 @@
       <c r="F221" t="n">
         <v>0.2528415918799355</v>
       </c>
+      <c r="G221" t="n">
+        <v>0.005050472678696493</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.005111531241509819</v>
+      </c>
+      <c r="I221" t="n">
+        <v>1.012089672927225</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0.01208967292722481</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5763,6 +8423,18 @@
       <c r="F222" t="n">
         <v>0.2142649556413497</v>
       </c>
+      <c r="G222" t="n">
+        <v>0.004911010603800755</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.005094265059532965</v>
+      </c>
+      <c r="I222" t="n">
+        <v>1.037315019354751</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0.03731501935475059</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5787,6 +8459,18 @@
       <c r="F223" t="n">
         <v>0.02272005392277237</v>
       </c>
+      <c r="G223" t="n">
+        <v>0.0039376495258709</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.003957074679222254</v>
+      </c>
+      <c r="I223" t="n">
+        <v>1.004933184942877</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0.004933184942877279</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5811,6 +8495,18 @@
       <c r="F224" t="n">
         <v>0.09122067984287162</v>
       </c>
+      <c r="G224" t="n">
+        <v>0.005550428596472127</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.005600163097482406</v>
+      </c>
+      <c r="I224" t="n">
+        <v>1.008960479383861</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0.008960479383860694</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5835,6 +8531,18 @@
       <c r="F225" t="n">
         <v>0.0335496862568451</v>
       </c>
+      <c r="G225" t="n">
+        <v>0.004365356433854312</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.004388769150882503</v>
+      </c>
+      <c r="I225" t="n">
+        <v>1.005363300198495</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0.005363300198494849</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5859,6 +8567,18 @@
       <c r="F226" t="n">
         <v>0.02160253069675195</v>
       </c>
+      <c r="G226" t="n">
+        <v>0.004692667953688796</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.004710106544323064</v>
+      </c>
+      <c r="I226" t="n">
+        <v>1.00371613564104</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0.003716135641039909</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5883,6 +8603,18 @@
       <c r="F227" t="n">
         <v>0.1651293148677624</v>
       </c>
+      <c r="G227" t="n">
+        <v>0.00391584148121049</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.003967969731343598</v>
+      </c>
+      <c r="I227" t="n">
+        <v>1.013312145137447</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0.01331214513744663</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5907,6 +8639,18 @@
       <c r="F228" t="n">
         <v>0.02352349864862119</v>
       </c>
+      <c r="G228" t="n">
+        <v>0.005139647608063529</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.005162042571177849</v>
+      </c>
+      <c r="I228" t="n">
+        <v>1.004357295445545</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0.004357295445544773</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5931,6 +8675,18 @@
       <c r="F229" t="n">
         <v>0.2191798929677518</v>
       </c>
+      <c r="G229" t="n">
+        <v>0.005462549792354581</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.006074732958187788</v>
+      </c>
+      <c r="I229" t="n">
+        <v>1.112069123230698</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0.1120691232306976</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5955,6 +8711,18 @@
       <c r="F230" t="n">
         <v>0.07084004336907102</v>
       </c>
+      <c r="G230" t="n">
+        <v>0.005761179069595813</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.005839732055267191</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1.013634880069244</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0.01363488006924418</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5979,6 +8747,18 @@
       <c r="F231" t="n">
         <v>0.09238956516113034</v>
       </c>
+      <c r="G231" t="n">
+        <v>0.004375243363112551</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.004501808656533491</v>
+      </c>
+      <c r="I231" t="n">
+        <v>1.028927600802279</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0.02892760080227884</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6003,6 +8783,18 @@
       <c r="F232" t="n">
         <v>0.07119663674712359</v>
       </c>
+      <c r="G232" t="n">
+        <v>0.006445789783713339</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.006622862490369359</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1.027471064461865</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0.02747106446186494</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6027,6 +8819,18 @@
       <c r="F233" t="n">
         <v>0.5509399236405417</v>
       </c>
+      <c r="G233" t="n">
+        <v>0.004151960693977624</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.004595264743068437</v>
+      </c>
+      <c r="I233" t="n">
+        <v>1.106769808715632</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0.1067698087156317</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6051,6 +8855,18 @@
       <c r="F234" t="n">
         <v>0.05884518969226905</v>
       </c>
+      <c r="G234" t="n">
+        <v>0.005673404964962771</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.005769229527052919</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1.016890132589147</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0.01689013258914723</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6075,6 +8891,18 @@
       <c r="F235" t="n">
         <v>0.05319176397558451</v>
       </c>
+      <c r="G235" t="n">
+        <v>0.003577666393808835</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.003602917895644172</v>
+      </c>
+      <c r="I235" t="n">
+        <v>1.007058092917505</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0.007058092917504828</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6099,6 +8927,18 @@
       <c r="F236" t="n">
         <v>0.353159608010241</v>
       </c>
+      <c r="G236" t="n">
+        <v>0.006317951777381817</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.006789581030984802</v>
+      </c>
+      <c r="I236" t="n">
+        <v>1.074649074608548</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0.07464907460854811</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6123,6 +8963,18 @@
       <c r="F237" t="n">
         <v>0.3301019459181783</v>
       </c>
+      <c r="G237" t="n">
+        <v>0.006185551968623893</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.006720064733328658</v>
+      </c>
+      <c r="I237" t="n">
+        <v>1.086413107094738</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0.08641310709473814</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6147,6 +8999,18 @@
       <c r="F238" t="n">
         <v>0.7747373393984736</v>
       </c>
+      <c r="G238" t="n">
+        <v>0.005883876754106828</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.006538806660858137</v>
+      </c>
+      <c r="I238" t="n">
+        <v>1.111309249687152</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0.1113092496871524</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6171,6 +9035,18 @@
       <c r="F239" t="n">
         <v>0.02759125564003393</v>
       </c>
+      <c r="G239" t="n">
+        <v>0.003778947951707784</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.003800480716455717</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1.005698084499471</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0.005698084499470858</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6195,6 +9071,18 @@
       <c r="F240" t="n">
         <v>0.0644324281016307</v>
       </c>
+      <c r="G240" t="n">
+        <v>0.005250663604717718</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.005492126135896274</v>
+      </c>
+      <c r="I240" t="n">
+        <v>1.04598705027715</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0.04598705027715021</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6219,6 +9107,18 @@
       <c r="F241" t="n">
         <v>0.08398978144646115</v>
       </c>
+      <c r="G241" t="n">
+        <v>0.004694868244160224</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.004913415074084537</v>
+      </c>
+      <c r="I241" t="n">
+        <v>1.04655015190174</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0.0465501519017399</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6243,6 +9143,18 @@
       <c r="F242" t="n">
         <v>0.1112458801174495</v>
       </c>
+      <c r="G242" t="n">
+        <v>0.005138552892880741</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.005430336230175769</v>
+      </c>
+      <c r="I242" t="n">
+        <v>1.056783172884973</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0.05678317288497357</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6267,6 +9179,18 @@
       <c r="F243" t="n">
         <v>0.0377334742029298</v>
       </c>
+      <c r="G243" t="n">
+        <v>0.002846645211120956</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0.002879280961633733</v>
+      </c>
+      <c r="I243" t="n">
+        <v>1.011464635770302</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0.01146463577030212</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6291,6 +9215,18 @@
       <c r="F244" t="n">
         <v>1.628892252118279</v>
       </c>
+      <c r="G244" t="n">
+        <v>0.007176569292617851</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.007712404071105673</v>
+      </c>
+      <c r="I244" t="n">
+        <v>1.074664474993505</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0.07466447499350518</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6315,6 +9251,18 @@
       <c r="F245" t="n">
         <v>0.07976008324403513</v>
       </c>
+      <c r="G245" t="n">
+        <v>0.005459266545598764</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0.005901200952537169</v>
+      </c>
+      <c r="I245" t="n">
+        <v>1.080951241938295</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0.08095124193829498</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6339,6 +9287,18 @@
       <c r="F246" t="n">
         <v>-0.003536999784461878</v>
       </c>
+      <c r="G246" t="n">
+        <v>0.005334194579540037</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0.005356052406721166</v>
+      </c>
+      <c r="I246" t="n">
+        <v>1.004097680887939</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0.004097680887939048</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6363,6 +9323,18 @@
       <c r="F247" t="n">
         <v>0.08639523745046425</v>
       </c>
+      <c r="G247" t="n">
+        <v>0.005146919433044001</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0.005456713107177455</v>
+      </c>
+      <c r="I247" t="n">
+        <v>1.060190115303638</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0.06019011530363809</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6387,6 +9359,18 @@
       <c r="F248" t="n">
         <v>0.01775827291474915</v>
       </c>
+      <c r="G248" t="n">
+        <v>0.005781911125811215</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0.005799246719251065</v>
+      </c>
+      <c r="I248" t="n">
+        <v>1.002998246265402</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0.002998246265401976</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6411,6 +9395,18 @@
       <c r="F249" t="n">
         <v>0.1019058428358448</v>
       </c>
+      <c r="G249" t="n">
+        <v>0.0004420650851949846</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0.0004508649001118008</v>
+      </c>
+      <c r="I249" t="n">
+        <v>1.019906152309981</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0.01990615230998135</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6435,6 +9431,18 @@
       <c r="F250" t="n">
         <v>0.06731597012894655</v>
       </c>
+      <c r="G250" t="n">
+        <v>0.0004986641415542902</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0.0005052253727137897</v>
+      </c>
+      <c r="I250" t="n">
+        <v>1.013157615743231</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0.01315761574323101</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6459,6 +9467,18 @@
       <c r="F251" t="n">
         <v>0.1721180165938858</v>
       </c>
+      <c r="G251" t="n">
+        <v>0.0006403291083923324</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.0006815245886722327</v>
+      </c>
+      <c r="I251" t="n">
+        <v>1.064334854905049</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0.06433485490504935</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6483,6 +9503,18 @@
       <c r="F252" t="n">
         <v>0.09054201698002723</v>
       </c>
+      <c r="G252" t="n">
+        <v>0.0006493376398557493</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0.0006587222713038042</v>
+      </c>
+      <c r="I252" t="n">
+        <v>1.014452621982825</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0.01445262198282508</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6507,6 +9539,18 @@
       <c r="F253" t="n">
         <v>0.08265880237756029</v>
       </c>
+      <c r="G253" t="n">
+        <v>0.0006015749282412745</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0.0006144370544930497</v>
+      </c>
+      <c r="I253" t="n">
+        <v>1.021380755161087</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0.02138075516108703</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6531,6 +9575,18 @@
       <c r="F254" t="n">
         <v>0.09879538330242466</v>
       </c>
+      <c r="G254" t="n">
+        <v>0.0005836421556877448</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0.0005922191368665492</v>
+      </c>
+      <c r="I254" t="n">
+        <v>1.014695616303962</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0.01469561630396204</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6555,6 +9611,18 @@
       <c r="F255" t="n">
         <v>0.3821720058417144</v>
       </c>
+      <c r="G255" t="n">
+        <v>0.000638291310593703</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0.0006903821387756818</v>
+      </c>
+      <c r="I255" t="n">
+        <v>1.081609803106244</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0.08160980310624441</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6579,6 +9647,18 @@
       <c r="F256" t="n">
         <v>0.1971217362196253</v>
       </c>
+      <c r="G256" t="n">
+        <v>0.0006177076902893538</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0.0006227131968527092</v>
+      </c>
+      <c r="I256" t="n">
+        <v>1.008103358015521</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0.008103358015521284</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6603,6 +9683,18 @@
       <c r="F257" t="n">
         <v>0.1444579390544902</v>
       </c>
+      <c r="G257" t="n">
+        <v>0.0007232682003385251</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0.0007701376007581644</v>
+      </c>
+      <c r="I257" t="n">
+        <v>1.064802241267765</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0.06480224126776507</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6627,6 +9719,18 @@
       <c r="F258" t="n">
         <v>0.07165653898839898</v>
       </c>
+      <c r="G258" t="n">
+        <v>0.000414580934952227</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0.0004169928432662186</v>
+      </c>
+      <c r="I258" t="n">
+        <v>1.005817701950693</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0.005817701950692848</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6651,6 +9755,18 @@
       <c r="F259" t="n">
         <v>0.2173318522588951</v>
       </c>
+      <c r="G259" t="n">
+        <v>0.000317182947517043</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0.0003243735761651243</v>
+      </c>
+      <c r="I259" t="n">
+        <v>1.022670287619088</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0.02267028761908753</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6675,6 +9791,18 @@
       <c r="F260" t="n">
         <v>0.6245123898870348</v>
       </c>
+      <c r="G260" t="n">
+        <v>0.0006743430273642813</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0.0007476428958495941</v>
+      </c>
+      <c r="I260" t="n">
+        <v>1.108698192923876</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0.1086981929238754</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6699,6 +9827,18 @@
       <c r="F261" t="n">
         <v>0.1298401804215344</v>
       </c>
+      <c r="G261" t="n">
+        <v>0.0006158296680252172</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0.0006196204911426375</v>
+      </c>
+      <c r="I261" t="n">
+        <v>1.006155635745151</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0.006155635745150666</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6723,6 +9863,18 @@
       <c r="F262" t="n">
         <v>0.1155724723537589</v>
       </c>
+      <c r="G262" t="n">
+        <v>0.0006033237990769868</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0.0006203097605114923</v>
+      </c>
+      <c r="I262" t="n">
+        <v>1.028153972146453</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0.02815397214645274</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6747,6 +9899,18 @@
       <c r="F263" t="n">
         <v>0.07217075480061401</v>
       </c>
+      <c r="G263" t="n">
+        <v>0.0006694389628454004</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0.0006773441242462647</v>
+      </c>
+      <c r="I263" t="n">
+        <v>1.011808636544345</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0.01180863654434462</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6771,6 +9935,18 @@
       <c r="F264" t="n">
         <v>0.1671573990927055</v>
       </c>
+      <c r="G264" t="n">
+        <v>0.0007802286702902619</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0.0008248271768986895</v>
+      </c>
+      <c r="I264" t="n">
+        <v>1.057160814908065</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0.05716081490806534</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6795,6 +9971,18 @@
       <c r="F265" t="n">
         <v>0.03712181317584327</v>
       </c>
+      <c r="G265" t="n">
+        <v>0.0005916282165933562</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0.0005958312188208079</v>
+      </c>
+      <c r="I265" t="n">
+        <v>1.007104127405642</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0.007104127405641676</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6819,6 +10007,18 @@
       <c r="F266" t="n">
         <v>0.1087900399328558</v>
       </c>
+      <c r="G266" t="n">
+        <v>0.0006045898807407096</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0.0006129754400675243</v>
+      </c>
+      <c r="I266" t="n">
+        <v>1.013869830762866</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0.01386983076286545</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6843,6 +10043,18 @@
       <c r="F267" t="n">
         <v>0.0365035824073203</v>
       </c>
+      <c r="G267" t="n">
+        <v>0.0005421742854388116</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0.0005461446070296539</v>
+      </c>
+      <c r="I267" t="n">
+        <v>1.007322961817765</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0.007322961817764815</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6867,6 +10079,18 @@
       <c r="F268" t="n">
         <v>0.2483202958731612</v>
       </c>
+      <c r="G268" t="n">
+        <v>0.0007044456015764035</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0.0007691813435449474</v>
+      </c>
+      <c r="I268" t="n">
+        <v>1.091896012727851</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0.0918960127278511</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6891,6 +10115,18 @@
       <c r="F269" t="n">
         <v>0.01136478255207218</v>
       </c>
+      <c r="G269" t="n">
+        <v>0.0005832298973790375</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.0005811306833935501</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0.9964007092316066</v>
+      </c>
+      <c r="J269" t="n">
+        <v>-0.003599290768393409</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6915,6 +10151,18 @@
       <c r="F270" t="n">
         <v>1.404876839277426</v>
       </c>
+      <c r="G270" t="n">
+        <v>0.0007176247217460078</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0.0007899293134998663</v>
+      </c>
+      <c r="I270" t="n">
+        <v>1.10075543604175</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0.10075543604175</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6939,6 +10187,18 @@
       <c r="F271" t="n">
         <v>1.334797139976013</v>
       </c>
+      <c r="G271" t="n">
+        <v>0.0007025750574206009</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.0008300536748255333</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1.181444837898104</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0.1814448378981045</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6963,6 +10223,18 @@
       <c r="F272" t="n">
         <v>0.362257029926892</v>
       </c>
+      <c r="G272" t="n">
+        <v>0.0006288150673342978</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.0006877706361000203</v>
+      </c>
+      <c r="I272" t="n">
+        <v>1.093756609579426</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0.09375660957942648</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6987,6 +10259,18 @@
       <c r="F273" t="n">
         <v>0.115011453737136</v>
       </c>
+      <c r="G273" t="n">
+        <v>0.0007002098386399395</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0.0007061369910543121</v>
+      </c>
+      <c r="I273" t="n">
+        <v>1.008464823096295</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0.00846482309629527</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7011,6 +10295,18 @@
       <c r="F274" t="n">
         <v>0.1185238140811029</v>
       </c>
+      <c r="G274" t="n">
+        <v>0.0006132652405759244</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0.0006546143021749603</v>
+      </c>
+      <c r="I274" t="n">
+        <v>1.067424433773883</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0.06742443377388303</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7035,6 +10331,18 @@
       <c r="F275" t="n">
         <v>0.1925443090190503</v>
       </c>
+      <c r="G275" t="n">
+        <v>0.0005232327210670607</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0.0005530701289963834</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1.057025118514135</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0.05702511851413544</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7059,6 +10367,18 @@
       <c r="F276" t="n">
         <v>1.244383406731956</v>
       </c>
+      <c r="G276" t="n">
+        <v>0.0008923004637561898</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0.0009668863105384938</v>
+      </c>
+      <c r="I276" t="n">
+        <v>1.083588264056628</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0.08358826405662804</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7083,6 +10403,18 @@
       <c r="F277" t="n">
         <v>0.2133857746511532</v>
       </c>
+      <c r="G277" t="n">
+        <v>0.0007613053082680187</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0.0008065135436419468</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1.059382530087407</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0.05938253008740671</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7107,6 +10439,18 @@
       <c r="F278" t="n">
         <v>0.3060716899471539</v>
       </c>
+      <c r="G278" t="n">
+        <v>0.0006849954598029368</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0.000716296142456151</v>
+      </c>
+      <c r="I278" t="n">
+        <v>1.045694730096779</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0.04569473009677893</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7131,6 +10475,18 @@
       <c r="F279" t="n">
         <v>0.4669530240221357</v>
       </c>
+      <c r="G279" t="n">
+        <v>0.0006193037107847044</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0.0006717938313535143</v>
+      </c>
+      <c r="I279" t="n">
+        <v>1.084756670523257</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0.08475667052325744</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7155,6 +10511,18 @@
       <c r="F280" t="n">
         <v>0.08352209274874292</v>
       </c>
+      <c r="G280" t="n">
+        <v>0.0005591339457766944</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0.0005889369318512928</v>
+      </c>
+      <c r="I280" t="n">
+        <v>1.053302050965979</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0.05330205096597913</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7179,6 +10547,18 @@
       <c r="F281" t="n">
         <v>0.01761000847271762</v>
       </c>
+      <c r="G281" t="n">
+        <v>0.0005562901953701689</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0.0005601316148783784</v>
+      </c>
+      <c r="I281" t="n">
+        <v>1.006905423716219</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0.006905423716219436</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -7203,6 +10583,18 @@
       <c r="F282" t="n">
         <v>0.4894105906892427</v>
       </c>
+      <c r="G282" t="n">
+        <v>0.0006610333655808375</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0.0006986849731920714</v>
+      </c>
+      <c r="I282" t="n">
+        <v>1.056958709759151</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0.0569587097591513</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -7227,6 +10619,18 @@
       <c r="F283" t="n">
         <v>0.04031286768270124</v>
       </c>
+      <c r="G283" t="n">
+        <v>0.0006231856873492574</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0.0006266732736008199</v>
+      </c>
+      <c r="I283" t="n">
+        <v>1.005596383746227</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0.005596383746226576</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -7251,6 +10655,18 @@
       <c r="F284" t="n">
         <v>0.05247220866211831</v>
       </c>
+      <c r="G284" t="n">
+        <v>0.0005835305330462864</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0.000588379931340438</v>
+      </c>
+      <c r="I284" t="n">
+        <v>1.008310444817404</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0.008310444817404141</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -7275,6 +10691,18 @@
       <c r="F285" t="n">
         <v>0.09235119367185043</v>
       </c>
+      <c r="G285" t="n">
+        <v>0.0004866432176399521</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0.0004913312701711342</v>
+      </c>
+      <c r="I285" t="n">
+        <v>1.00963344882092</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0.009633448820919514</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7299,6 +10727,18 @@
       <c r="F286" t="n">
         <v>0.03245466652774558</v>
       </c>
+      <c r="G286" t="n">
+        <v>0.0006749395520084122</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0.0006799212770168233</v>
+      </c>
+      <c r="I286" t="n">
+        <v>1.007380994332881</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0.007380994332880647</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7323,6 +10763,18 @@
       <c r="F287" t="n">
         <v>0.4156766635738067</v>
       </c>
+      <c r="G287" t="n">
+        <v>0.0005265492201127387</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0.0005306746628627107</v>
+      </c>
+      <c r="I287" t="n">
+        <v>1.007834866319028</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0.007834866319028459</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7347,6 +10799,18 @@
       <c r="F288" t="n">
         <v>0.5846031322138844</v>
       </c>
+      <c r="G288" t="n">
+        <v>0.0005832186813310263</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0.0006207030761151278</v>
+      </c>
+      <c r="I288" t="n">
+        <v>1.064271594830526</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0.06427159483052625</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7371,6 +10835,18 @@
       <c r="F289" t="n">
         <v>0.09812561102139698</v>
       </c>
+      <c r="G289" t="n">
+        <v>0.0003208781337884773</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0.0003250425770816046</v>
+      </c>
+      <c r="I289" t="n">
+        <v>1.012978270734622</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0.01297827073462231</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7395,6 +10871,18 @@
       <c r="F290" t="n">
         <v>0.1136253330661948</v>
       </c>
+      <c r="G290" t="n">
+        <v>0.0006847897200825459</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0.0007046021547595922</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1.028932143833377</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0.0289321438333772</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7419,6 +10907,18 @@
       <c r="F291" t="n">
         <v>0.1777807295092858</v>
       </c>
+      <c r="G291" t="n">
+        <v>0.0006567696396822965</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0.0006714195166934056</v>
+      </c>
+      <c r="I291" t="n">
+        <v>1.022305959541912</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0.02230595954191162</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7443,6 +10943,18 @@
       <c r="F292" t="n">
         <v>0.07209618168537038</v>
       </c>
+      <c r="G292" t="n">
+        <v>0.0007704469398817117</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0.0008055401991936676</v>
+      </c>
+      <c r="I292" t="n">
+        <v>1.045549222789234</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0.04554922278923438</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7467,6 +10979,18 @@
       <c r="F293" t="n">
         <v>0.06881299961209622</v>
       </c>
+      <c r="G293" t="n">
+        <v>0.0006703025268186097</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0.0006882758117776468</v>
+      </c>
+      <c r="I293" t="n">
+        <v>1.026813691191561</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0.02681369119156075</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7491,6 +11015,18 @@
       <c r="F294" t="n">
         <v>0.4172647867658223</v>
       </c>
+      <c r="G294" t="n">
+        <v>0.0006499109273064198</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0.0007063027194654107</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1.086768493634518</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0.08676849363451818</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -7515,6 +11051,18 @@
       <c r="F295" t="n">
         <v>0.08110050124955545</v>
       </c>
+      <c r="G295" t="n">
+        <v>0.0006810135056489959</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0.0007149845165983227</v>
+      </c>
+      <c r="I295" t="n">
+        <v>1.049883020920346</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0.04988302092034563</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7539,6 +11087,18 @@
       <c r="F296" t="n">
         <v>0.0741090623557587</v>
       </c>
+      <c r="G296" t="n">
+        <v>0.0004829487140965973</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0.0004897508314696561</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1.014084554269459</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0.01408455426945875</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7563,6 +11123,18 @@
       <c r="F297" t="n">
         <v>0.2106104651680059</v>
       </c>
+      <c r="G297" t="n">
+        <v>0.0006794815147323933</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0.0007267851314885458</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1.069617223913417</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0.0696172239134166</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7587,6 +11159,18 @@
       <c r="F298" t="n">
         <v>0.04808488329503931</v>
       </c>
+      <c r="G298" t="n">
+        <v>0.0006920095422884897</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0.0006992045791360892</v>
+      </c>
+      <c r="I298" t="n">
+        <v>1.010397308718902</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0.01039730871890201</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7611,6 +11195,18 @@
       <c r="F299" t="n">
         <v>0.7567384730951878</v>
       </c>
+      <c r="G299" t="n">
+        <v>0.0006470235848458918</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0.0007588187962074803</v>
+      </c>
+      <c r="I299" t="n">
+        <v>1.172783827328668</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0.1727838273286683</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7635,6 +11231,18 @@
       <c r="F300" t="n">
         <v>1.291576356144434</v>
       </c>
+      <c r="G300" t="n">
+        <v>0.0004864589950853067</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0.0005261077785581963</v>
+      </c>
+      <c r="I300" t="n">
+        <v>1.081504882988003</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0.08150488298800326</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7659,6 +11267,18 @@
       <c r="F301" t="n">
         <v>0.05366655530402923</v>
       </c>
+      <c r="G301" t="n">
+        <v>0.0004617479985002741</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0.0004651163141044758</v>
+      </c>
+      <c r="I301" t="n">
+        <v>1.007294705369902</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0.007294705369902409</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7683,6 +11303,18 @@
       <c r="F302" t="n">
         <v>0.1275175644163128</v>
       </c>
+      <c r="G302" t="n">
+        <v>0.0006341617200981855</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0.0006410366862592104</v>
+      </c>
+      <c r="I302" t="n">
+        <v>1.010841029887393</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0.01084102988739289</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7707,6 +11339,18 @@
       <c r="F303" t="n">
         <v>0.2911516072102299</v>
       </c>
+      <c r="G303" t="n">
+        <v>0.0006613326584558226</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0.0007460763265218266</v>
+      </c>
+      <c r="I303" t="n">
+        <v>1.128140757881028</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0.1281407578810279</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7731,6 +11375,18 @@
       <c r="F304" t="n">
         <v>0.1014330765367046</v>
       </c>
+      <c r="G304" t="n">
+        <v>0.0004918499420682077</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0.0004986055556630968</v>
+      </c>
+      <c r="I304" t="n">
+        <v>1.013735111091977</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0.01373511109197661</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7755,6 +11411,18 @@
       <c r="F305" t="n">
         <v>0.3561208683386628</v>
       </c>
+      <c r="G305" t="n">
+        <v>0.0006245220505577281</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0.000649152953833735</v>
+      </c>
+      <c r="I305" t="n">
+        <v>1.039439605461505</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0.03943960546150509</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7779,6 +11447,18 @@
       <c r="F306" t="n">
         <v>0.2900399689325567</v>
       </c>
+      <c r="G306" t="n">
+        <v>0.000682204517822094</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0.0006921291727320023</v>
+      </c>
+      <c r="I306" t="n">
+        <v>1.014547917304319</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0.01454791730431855</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7803,6 +11483,18 @@
       <c r="F307" t="n">
         <v>0.1643699140724023</v>
       </c>
+      <c r="G307" t="n">
+        <v>0.0007117122951111342</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0.0007576085709311896</v>
+      </c>
+      <c r="I307" t="n">
+        <v>1.064487119493824</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0.06448711949382395</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7827,6 +11519,18 @@
       <c r="F308" t="n">
         <v>0.01175170501304355</v>
       </c>
+      <c r="G308" t="n">
+        <v>0.0007367997844332595</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0.0007417273209621032</v>
+      </c>
+      <c r="I308" t="n">
+        <v>1.006687755117401</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0.006687755117401376</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7851,6 +11555,18 @@
       <c r="F309" t="n">
         <v>0.07552675406388816</v>
       </c>
+      <c r="G309" t="n">
+        <v>0.000675623227802576</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0.000691273786788596</v>
+      </c>
+      <c r="I309" t="n">
+        <v>1.023164625403603</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0.02316462540360327</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7875,6 +11591,18 @@
       <c r="F310" t="n">
         <v>0.05264103207490767</v>
       </c>
+      <c r="G310" t="n">
+        <v>0.0006313282117531919</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0.0006364086074031307</v>
+      </c>
+      <c r="I310" t="n">
+        <v>1.008047154483768</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0.008047154483767761</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7899,6 +11627,18 @@
       <c r="F311" t="n">
         <v>0.3599959134789827</v>
       </c>
+      <c r="G311" t="n">
+        <v>0.0007255197672017526</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0.0007650208646468192</v>
+      </c>
+      <c r="I311" t="n">
+        <v>1.054445239441811</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0.0544452394418113</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7923,6 +11663,18 @@
       <c r="F312" t="n">
         <v>0.6703100565346127</v>
       </c>
+      <c r="G312" t="n">
+        <v>0.0006222373616250274</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0.0006631065186677188</v>
+      </c>
+      <c r="I312" t="n">
+        <v>1.065680975722766</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0.06568097572276596</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7947,6 +11699,18 @@
       <c r="F313" t="n">
         <v>0.09380982556209845</v>
       </c>
+      <c r="G313" t="n">
+        <v>0.000643648963158489</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0.0006510351593958654</v>
+      </c>
+      <c r="I313" t="n">
+        <v>1.011475503978335</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0.01147550397833503</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7971,6 +11735,18 @@
       <c r="F314" t="n">
         <v>0.3612981988739096</v>
       </c>
+      <c r="G314" t="n">
+        <v>0.0004553499813277047</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0.0004985771405940533</v>
+      </c>
+      <c r="I314" t="n">
+        <v>1.094931725132188</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0.09493172513218801</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7995,6 +11771,18 @@
       <c r="F315" t="n">
         <v>0.1665395146093718</v>
       </c>
+      <c r="G315" t="n">
+        <v>0.000783407733940444</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0.0008391383205517592</v>
+      </c>
+      <c r="I315" t="n">
+        <v>1.071138673001091</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0.07113867300109136</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -8019,6 +11807,18 @@
       <c r="F316" t="n">
         <v>0.07208643536550474</v>
       </c>
+      <c r="G316" t="n">
+        <v>0.0005035068512081662</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0.000507132115481457</v>
+      </c>
+      <c r="I316" t="n">
+        <v>1.00720002968101</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0.007200029681010231</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -8043,6 +11843,18 @@
       <c r="F317" t="n">
         <v>0.2344706498934645</v>
       </c>
+      <c r="G317" t="n">
+        <v>0.0007263748828935426</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0.0007610475612705825</v>
+      </c>
+      <c r="I317" t="n">
+        <v>1.047733861940435</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0.04773386194043485</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -8067,6 +11879,18 @@
       <c r="F318" t="n">
         <v>0.07191153623627099</v>
       </c>
+      <c r="G318" t="n">
+        <v>0.0005697239142832948</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0.0005747475703073156</v>
+      </c>
+      <c r="I318" t="n">
+        <v>1.0088177025715</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0.008817702571500002</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -8091,6 +11915,18 @@
       <c r="F319" t="n">
         <v>0.4861052330092998</v>
       </c>
+      <c r="G319" t="n">
+        <v>0.00055221768081488</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0.0006159506671381976</v>
+      </c>
+      <c r="I319" t="n">
+        <v>1.115412795601311</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0.1154127956013109</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -8115,6 +11951,18 @@
       <c r="F320" t="n">
         <v>0.6184063058834371</v>
       </c>
+      <c r="G320" t="n">
+        <v>0.0007126010642050339</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0.000794542695677032</v>
+      </c>
+      <c r="I320" t="n">
+        <v>1.114989487930966</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0.1149894879309658</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -8139,6 +11987,18 @@
       <c r="F321" t="n">
         <v>0.2023120155928038</v>
       </c>
+      <c r="G321" t="n">
+        <v>0.0007325611260793426</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0.0007675727241927047</v>
+      </c>
+      <c r="I321" t="n">
+        <v>1.047793415275451</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0.04779341527545117</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -8163,6 +12023,18 @@
       <c r="F322" t="n">
         <v>0.5096238026300677</v>
       </c>
+      <c r="G322" t="n">
+        <v>0.000661777725656915</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0.0007021020630056421</v>
+      </c>
+      <c r="I322" t="n">
+        <v>1.060933355393156</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0.06093335539315568</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -8187,6 +12059,18 @@
       <c r="F323" t="n">
         <v>-0.03023419919181974</v>
       </c>
+      <c r="G323" t="n">
+        <v>0.0005367067352049193</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0.0005351902292642193</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0.99717442349569</v>
+      </c>
+      <c r="J323" t="n">
+        <v>-0.002825576504309989</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -8211,6 +12095,18 @@
       <c r="F324" t="n">
         <v>0.1020485057554632</v>
       </c>
+      <c r="G324" t="n">
+        <v>0.0004030638560671585</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0.0004072332403790405</v>
+      </c>
+      <c r="I324" t="n">
+        <v>1.010344227717574</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0.01034422771757363</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -8235,6 +12131,18 @@
       <c r="F325" t="n">
         <v>0.2293519956583408</v>
       </c>
+      <c r="G325" t="n">
+        <v>0.0004675410622300316</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0.0004748469786849275</v>
+      </c>
+      <c r="I325" t="n">
+        <v>1.015626256269447</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0.01562625626944702</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -8259,6 +12167,18 @@
       <c r="F326" t="n">
         <v>0.1266688007524605</v>
       </c>
+      <c r="G326" t="n">
+        <v>0.0004283589652017366</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0.0004325528922586724</v>
+      </c>
+      <c r="I326" t="n">
+        <v>1.009790683509941</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0.009790683509940506</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -8283,6 +12203,18 @@
       <c r="F327" t="n">
         <v>0.1661500095888133</v>
       </c>
+      <c r="G327" t="n">
+        <v>0.0005804215246570346</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0.0005848853962742873</v>
+      </c>
+      <c r="I327" t="n">
+        <v>1.0076907410005</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0.007690741000500162</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -8307,6 +12239,18 @@
       <c r="F328" t="n">
         <v>0.1545665552060413</v>
       </c>
+      <c r="G328" t="n">
+        <v>0.0006884911945437299</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0.000701403994083862</v>
+      </c>
+      <c r="I328" t="n">
+        <v>1.018755213781186</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0.01875521378118638</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -8331,6 +12275,18 @@
       <c r="F329" t="n">
         <v>0.03224142192588263</v>
       </c>
+      <c r="G329" t="n">
+        <v>0.0005534775352102443</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0.0005575692088800212</v>
+      </c>
+      <c r="I329" t="n">
+        <v>1.007392664398244</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0.007392664398244475</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -8355,6 +12311,18 @@
       <c r="F330" t="n">
         <v>0.06137259956600723</v>
       </c>
+      <c r="G330" t="n">
+        <v>0.0006906241382762712</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0.000721997529354362</v>
+      </c>
+      <c r="I330" t="n">
+        <v>1.04542759127475</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0.04542759127474992</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -8379,6 +12347,18 @@
       <c r="F331" t="n">
         <v>0.339373464319034</v>
       </c>
+      <c r="G331" t="n">
+        <v>0.0004903453395273709</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0.0005402936878696395</v>
+      </c>
+      <c r="I331" t="n">
+        <v>1.101863613897936</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0.1018636138979361</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -8403,6 +12383,18 @@
       <c r="F332" t="n">
         <v>0.08007544313820464</v>
       </c>
+      <c r="G332" t="n">
+        <v>0.0007357393474824864</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0.0007964716560423414</v>
+      </c>
+      <c r="I332" t="n">
+        <v>1.082545957026311</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0.0825459570263105</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -8427,6 +12419,18 @@
       <c r="F333" t="n">
         <v>0.07969934083466322</v>
       </c>
+      <c r="G333" t="n">
+        <v>0.0007348647339950579</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0.0007955365368605673</v>
+      </c>
+      <c r="I333" t="n">
+        <v>1.082561864869566</v>
+      </c>
+      <c r="J333" t="n">
+        <v>0.08256186486956583</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -8451,6 +12455,18 @@
       <c r="F334" t="n">
         <v>0.1492453018312798</v>
       </c>
+      <c r="G334" t="n">
+        <v>0.0006299009052370334</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0.0006355613082794558</v>
+      </c>
+      <c r="I334" t="n">
+        <v>1.008986180199713</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0.008986180199713041</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -8475,6 +12491,18 @@
       <c r="F335" t="n">
         <v>0.1642485380437892</v>
       </c>
+      <c r="G335" t="n">
+        <v>0.0006647880764964235</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0.0007044797911593915</v>
+      </c>
+      <c r="I335" t="n">
+        <v>1.059705816133394</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0.05970581613339385</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -8499,6 +12527,18 @@
       <c r="F336" t="n">
         <v>0.07898585698673607</v>
       </c>
+      <c r="G336" t="n">
+        <v>0.000655816326093311</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0.0006705390976850043</v>
+      </c>
+      <c r="I336" t="n">
+        <v>1.022449535038868</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0.02244953503886777</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -8523,6 +12563,18 @@
       <c r="F337" t="n">
         <v>0.3567142755518891</v>
       </c>
+      <c r="G337" t="n">
+        <v>0.0004624410943794617</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0.0004661818733555686</v>
+      </c>
+      <c r="I337" t="n">
+        <v>1.008089201028136</v>
+      </c>
+      <c r="J337" t="n">
+        <v>0.00808920102813645</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -8547,6 +12599,18 @@
       <c r="F338" t="n">
         <v>0.4638311890251676</v>
       </c>
+      <c r="G338" t="n">
+        <v>0.0007790495338371898</v>
+      </c>
+      <c r="H338" t="n">
+        <v>0.0008413728772877093</v>
+      </c>
+      <c r="I338" t="n">
+        <v>1.07999920511286</v>
+      </c>
+      <c r="J338" t="n">
+        <v>0.07999920511286027</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -8571,6 +12635,18 @@
       <c r="F339" t="n">
         <v>0.4969198246534837</v>
       </c>
+      <c r="G339" t="n">
+        <v>0.0005830303819547316</v>
+      </c>
+      <c r="H339" t="n">
+        <v>0.0006611459991356838</v>
+      </c>
+      <c r="I339" t="n">
+        <v>1.133982069543363</v>
+      </c>
+      <c r="J339" t="n">
+        <v>0.1339820695433628</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -8595,6 +12671,18 @@
       <c r="F340" t="n">
         <v>0.09411627129095435</v>
       </c>
+      <c r="G340" t="n">
+        <v>0.0005123892268571852</v>
+      </c>
+      <c r="H340" t="n">
+        <v>0.0005195952494665186</v>
+      </c>
+      <c r="I340" t="n">
+        <v>1.014063571659249</v>
+      </c>
+      <c r="J340" t="n">
+        <v>0.01406357165924937</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -8619,6 +12707,18 @@
       <c r="F341" t="n">
         <v>0.05749408789721037</v>
       </c>
+      <c r="G341" t="n">
+        <v>0.0006584481159817252</v>
+      </c>
+      <c r="H341" t="n">
+        <v>0.0006885381551480065</v>
+      </c>
+      <c r="I341" t="n">
+        <v>1.045698420932404</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0.04569842093240409</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -8643,6 +12743,18 @@
       <c r="F342" t="n">
         <v>0.06802457321596909</v>
       </c>
+      <c r="G342" t="n">
+        <v>0.0004645718899767051</v>
+      </c>
+      <c r="H342" t="n">
+        <v>0.0004705755781355769</v>
+      </c>
+      <c r="I342" t="n">
+        <v>1.01292305515767</v>
+      </c>
+      <c r="J342" t="n">
+        <v>0.01292305515766971</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -8667,6 +12779,18 @@
       <c r="F343" t="n">
         <v>0.1026240336489873</v>
       </c>
+      <c r="G343" t="n">
+        <v>0.0006001676557078387</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0.0006233216181767857</v>
+      </c>
+      <c r="I343" t="n">
+        <v>1.038579157421669</v>
+      </c>
+      <c r="J343" t="n">
+        <v>0.03857915742166947</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8691,6 +12815,18 @@
       <c r="F344" t="n">
         <v>1.801844516354535</v>
       </c>
+      <c r="G344" t="n">
+        <v>0.0005252168727377115</v>
+      </c>
+      <c r="H344" t="n">
+        <v>0.0007406553324217535</v>
+      </c>
+      <c r="I344" t="n">
+        <v>1.410189525254704</v>
+      </c>
+      <c r="J344" t="n">
+        <v>0.4101895252547036</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8715,6 +12851,18 @@
       <c r="F345" t="n">
         <v>0.1384931006134136</v>
       </c>
+      <c r="G345" t="n">
+        <v>0.0005859442947649501</v>
+      </c>
+      <c r="H345" t="n">
+        <v>0.000589647674405818</v>
+      </c>
+      <c r="I345" t="n">
+        <v>1.006320361293651</v>
+      </c>
+      <c r="J345" t="n">
+        <v>0.00632036129365074</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8739,6 +12887,18 @@
       <c r="F346" t="n">
         <v>0.1135169585091238</v>
       </c>
+      <c r="G346" t="n">
+        <v>0.0007168212188674179</v>
+      </c>
+      <c r="H346" t="n">
+        <v>0.000724791565253022</v>
+      </c>
+      <c r="I346" t="n">
+        <v>1.011119015698499</v>
+      </c>
+      <c r="J346" t="n">
+        <v>0.01111901569849922</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8763,6 +12923,18 @@
       <c r="F347" t="n">
         <v>0.3170748061356191</v>
       </c>
+      <c r="G347" t="n">
+        <v>0.0006096171913233069</v>
+      </c>
+      <c r="H347" t="n">
+        <v>0.0006398715461932805</v>
+      </c>
+      <c r="I347" t="n">
+        <v>1.049628447656307</v>
+      </c>
+      <c r="J347" t="n">
+        <v>0.04962844765630685</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8787,6 +12959,18 @@
       <c r="F348" t="n">
         <v>0.1267999166478122</v>
       </c>
+      <c r="G348" t="n">
+        <v>0.0007472789229030983</v>
+      </c>
+      <c r="H348" t="n">
+        <v>0.0007560700882125465</v>
+      </c>
+      <c r="I348" t="n">
+        <v>1.01176423560201</v>
+      </c>
+      <c r="J348" t="n">
+        <v>0.0117642356020098</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8811,6 +12995,18 @@
       <c r="F349" t="n">
         <v>2.35026156937831</v>
       </c>
+      <c r="G349" t="n">
+        <v>0.0005661101388861839</v>
+      </c>
+      <c r="H349" t="n">
+        <v>0.0007228223020136429</v>
+      </c>
+      <c r="I349" t="n">
+        <v>1.276822745898508</v>
+      </c>
+      <c r="J349" t="n">
+        <v>0.2768227458985076</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8835,6 +13031,18 @@
       <c r="F350" t="n">
         <v>0.1628043540625402</v>
       </c>
+      <c r="G350" t="n">
+        <v>0.0005664218967901771</v>
+      </c>
+      <c r="H350" t="n">
+        <v>0.0005725536085874779</v>
+      </c>
+      <c r="I350" t="n">
+        <v>1.010825343850667</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0.01082534385066726</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8859,6 +13067,18 @@
       <c r="F351" t="n">
         <v>0.01753321537638886</v>
       </c>
+      <c r="G351" t="n">
+        <v>0.0007501738042427516</v>
+      </c>
+      <c r="H351" t="n">
+        <v>0.000756311539319706</v>
+      </c>
+      <c r="I351" t="n">
+        <v>1.008181750738617</v>
+      </c>
+      <c r="J351" t="n">
+        <v>0.008181750738617202</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8883,6 +13103,18 @@
       <c r="F352" t="n">
         <v>0.01846966174899188</v>
       </c>
+      <c r="G352" t="n">
+        <v>0.0008528747464554386</v>
+      </c>
+      <c r="H352" t="n">
+        <v>0.0008599624653124954</v>
+      </c>
+      <c r="I352" t="n">
+        <v>1.008310386591365</v>
+      </c>
+      <c r="J352" t="n">
+        <v>0.008310386591364649</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8907,6 +13139,18 @@
       <c r="F353" t="n">
         <v>3.183931347705154</v>
       </c>
+      <c r="G353" t="n">
+        <v>0.0008376680095307456</v>
+      </c>
+      <c r="H353" t="n">
+        <v>0.0009481472403230375</v>
+      </c>
+      <c r="I353" t="n">
+        <v>1.131889041404579</v>
+      </c>
+      <c r="J353" t="n">
+        <v>0.1318890414045791</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8931,6 +13175,18 @@
       <c r="F354" t="n">
         <v>0.6651042318161958</v>
       </c>
+      <c r="G354" t="n">
+        <v>0.0005064969680191703</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0.0005520532502510057</v>
+      </c>
+      <c r="I354" t="n">
+        <v>1.089943839960186</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0.08994383996018547</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8955,6 +13211,18 @@
       <c r="F355" t="n">
         <v>0.7068861257017814</v>
       </c>
+      <c r="G355" t="n">
+        <v>0.0006204841155205141</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0.0006928490484910074</v>
+      </c>
+      <c r="I355" t="n">
+        <v>1.11662656812703</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0.1166265681270302</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8979,6 +13247,18 @@
       <c r="F356" t="n">
         <v>0.1165792527491003</v>
       </c>
+      <c r="G356" t="n">
+        <v>0.0007470306641337032</v>
+      </c>
+      <c r="H356" t="n">
+        <v>0.0007600047578240485</v>
+      </c>
+      <c r="I356" t="n">
+        <v>1.017367551712741</v>
+      </c>
+      <c r="J356" t="n">
+        <v>0.01736755171274097</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -9003,6 +13283,18 @@
       <c r="F357" t="n">
         <v>0.109371673078802</v>
       </c>
+      <c r="G357" t="n">
+        <v>0.0005241823000479661</v>
+      </c>
+      <c r="H357" t="n">
+        <v>0.0005488922725561833</v>
+      </c>
+      <c r="I357" t="n">
+        <v>1.047140036025551</v>
+      </c>
+      <c r="J357" t="n">
+        <v>0.04714003602555084</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -9027,6 +13319,18 @@
       <c r="F358" t="n">
         <v>0.2397941290873563</v>
       </c>
+      <c r="G358" t="n">
+        <v>0.0007372353811042312</v>
+      </c>
+      <c r="H358" t="n">
+        <v>0.0007629780367274344</v>
+      </c>
+      <c r="I358" t="n">
+        <v>1.034917824460142</v>
+      </c>
+      <c r="J358" t="n">
+        <v>0.03491782446014172</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -9051,6 +13355,18 @@
       <c r="F359" t="n">
         <v>0.1854608356299225</v>
       </c>
+      <c r="G359" t="n">
+        <v>0.0006610184748077412</v>
+      </c>
+      <c r="H359" t="n">
+        <v>0.0007300714667543399</v>
+      </c>
+      <c r="I359" t="n">
+        <v>1.104464541579845</v>
+      </c>
+      <c r="J359" t="n">
+        <v>0.1044645415798446</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -9075,6 +13391,18 @@
       <c r="F360" t="n">
         <v>0.7358314453264823</v>
       </c>
+      <c r="G360" t="n">
+        <v>0.0004133921120033722</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0.0004735147971005171</v>
+      </c>
+      <c r="I360" t="n">
+        <v>1.145437426964389</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0.145437426964389</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -9099,6 +13427,18 @@
       <c r="F361" t="n">
         <v>0.09202410924336499</v>
       </c>
+      <c r="G361" t="n">
+        <v>0.0003817306182613467</v>
+      </c>
+      <c r="H361" t="n">
+        <v>0.0003872559105319806</v>
+      </c>
+      <c r="I361" t="n">
+        <v>1.014474323007674</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0.01447432300767417</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -9123,6 +13463,18 @@
       <c r="F362" t="n">
         <v>0.08281222706218251</v>
       </c>
+      <c r="G362" t="n">
+        <v>0.0006070593652590545</v>
+      </c>
+      <c r="H362" t="n">
+        <v>0.0006135196327433794</v>
+      </c>
+      <c r="I362" t="n">
+        <v>1.010641903994955</v>
+      </c>
+      <c r="J362" t="n">
+        <v>0.01064190399495446</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -9147,6 +13499,18 @@
       <c r="F363" t="n">
         <v>0.1578426273617812</v>
       </c>
+      <c r="G363" t="n">
+        <v>0.0005440017919316922</v>
+      </c>
+      <c r="H363" t="n">
+        <v>0.000571836354488352</v>
+      </c>
+      <c r="I363" t="n">
+        <v>1.051166306746568</v>
+      </c>
+      <c r="J363" t="n">
+        <v>0.05116630674656833</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -9171,6 +13535,18 @@
       <c r="F364" t="n">
         <v>0.373359287573282</v>
       </c>
+      <c r="G364" t="n">
+        <v>0.0006139159084475482</v>
+      </c>
+      <c r="H364" t="n">
+        <v>0.0006383804697731057</v>
+      </c>
+      <c r="I364" t="n">
+        <v>1.039850020155729</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0.03985002015572906</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -9195,6 +13571,18 @@
       <c r="F365" t="n">
         <v>0.04108749070861806</v>
       </c>
+      <c r="G365" t="n">
+        <v>0.0005091599674002433</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0.0005125719170343283</v>
+      </c>
+      <c r="I365" t="n">
+        <v>1.006701134913466</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0.00670113491346615</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -9219,6 +13607,18 @@
       <c r="F366" t="n">
         <v>0.5991460768832745</v>
       </c>
+      <c r="G366" t="n">
+        <v>0.0007216589324866878</v>
+      </c>
+      <c r="H366" t="n">
+        <v>0.0007790831705338082</v>
+      </c>
+      <c r="I366" t="n">
+        <v>1.079572545231649</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0.07957254523164881</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -9243,6 +13643,18 @@
       <c r="F367" t="n">
         <v>0.09338556384047665</v>
       </c>
+      <c r="G367" t="n">
+        <v>0.0003795941992188109</v>
+      </c>
+      <c r="H367" t="n">
+        <v>0.0003831143930506225</v>
+      </c>
+      <c r="I367" t="n">
+        <v>1.009273571195387</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0.009273571195387029</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -9267,6 +13679,18 @@
       <c r="F368" t="n">
         <v>0.2730039377750417</v>
       </c>
+      <c r="G368" t="n">
+        <v>0.0006506678943605101</v>
+      </c>
+      <c r="H368" t="n">
+        <v>0.0006629841494592958</v>
+      </c>
+      <c r="I368" t="n">
+        <v>1.018928635031071</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0.01892863503107121</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -9291,6 +13715,18 @@
       <c r="F369" t="n">
         <v>0.05615607969945433</v>
       </c>
+      <c r="G369" t="n">
+        <v>0.0004638873063506731</v>
+      </c>
+      <c r="H369" t="n">
+        <v>0.0004685511976368339</v>
+      </c>
+      <c r="I369" t="n">
+        <v>1.010053931681923</v>
+      </c>
+      <c r="J369" t="n">
+        <v>0.01005393168192263</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -9315,6 +13751,18 @@
       <c r="F370" t="n">
         <v>0.0710301931196544</v>
       </c>
+      <c r="G370" t="n">
+        <v>0.0006413784540472928</v>
+      </c>
+      <c r="H370" t="n">
+        <v>0.0006617185440370362</v>
+      </c>
+      <c r="I370" t="n">
+        <v>1.031713085872142</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0.03171308587214187</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -9339,6 +13787,18 @@
       <c r="F371" t="n">
         <v>0.1264986916712339</v>
       </c>
+      <c r="G371" t="n">
+        <v>0.0006074846360562075</v>
+      </c>
+      <c r="H371" t="n">
+        <v>0.0006394208128811772</v>
+      </c>
+      <c r="I371" t="n">
+        <v>1.05257116794311</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0.05257116794310959</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -9363,6 +13823,18 @@
       <c r="F372" t="n">
         <v>0.08143290839990423</v>
       </c>
+      <c r="G372" t="n">
+        <v>0.0005809747803390375</v>
+      </c>
+      <c r="H372" t="n">
+        <v>0.0006083958902832241</v>
+      </c>
+      <c r="I372" t="n">
+        <v>1.047198451416746</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0.04719845141674574</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -9387,6 +13859,18 @@
       <c r="F373" t="n">
         <v>0.1011542915970612</v>
       </c>
+      <c r="G373" t="n">
+        <v>0.0006655206565253882</v>
+      </c>
+      <c r="H373" t="n">
+        <v>0.0007029527412800083</v>
+      </c>
+      <c r="I373" t="n">
+        <v>1.05624481282076</v>
+      </c>
+      <c r="J373" t="n">
+        <v>0.05624481282076051</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -9411,6 +13895,18 @@
       <c r="F374" t="n">
         <v>0.5855323881314161</v>
       </c>
+      <c r="G374" t="n">
+        <v>0.0006353035596233265</v>
+      </c>
+      <c r="H374" t="n">
+        <v>0.0006727835623763322</v>
+      </c>
+      <c r="I374" t="n">
+        <v>1.058995423817911</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0.05899542381791114</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -9435,6 +13931,18 @@
       <c r="F375" t="n">
         <v>0.3632455146447837</v>
       </c>
+      <c r="G375" t="n">
+        <v>0.0006770289137177979</v>
+      </c>
+      <c r="H375" t="n">
+        <v>0.0007025317782937336</v>
+      </c>
+      <c r="I375" t="n">
+        <v>1.037668796796123</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0.03766879679612303</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -9459,6 +13967,18 @@
       <c r="F376" t="n">
         <v>0.1699488318189414</v>
       </c>
+      <c r="G376" t="n">
+        <v>0.000756722760403066</v>
+      </c>
+      <c r="H376" t="n">
+        <v>0.0007926279167174579</v>
+      </c>
+      <c r="I376" t="n">
+        <v>1.047448230968059</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0.04744823096805909</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -9483,6 +14003,18 @@
       <c r="F377" t="n">
         <v>0.1362653810929691</v>
       </c>
+      <c r="G377" t="n">
+        <v>0.0006359461314421073</v>
+      </c>
+      <c r="H377" t="n">
+        <v>0.0006551160273921209</v>
+      </c>
+      <c r="I377" t="n">
+        <v>1.030143898991166</v>
+      </c>
+      <c r="J377" t="n">
+        <v>0.0301438989911659</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -9507,6 +14039,18 @@
       <c r="F378" t="n">
         <v>0.3059738252564836</v>
       </c>
+      <c r="G378" t="n">
+        <v>0.0006749986320485176</v>
+      </c>
+      <c r="H378" t="n">
+        <v>0.0007258853423868031</v>
+      </c>
+      <c r="I378" t="n">
+        <v>1.07538787180035</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0.0753878718003503</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -9531,6 +14075,18 @@
       <c r="F379" t="n">
         <v>0.1470229807995797</v>
       </c>
+      <c r="G379" t="n">
+        <v>0.0005768308067477347</v>
+      </c>
+      <c r="H379" t="n">
+        <v>0.0005955717118828229</v>
+      </c>
+      <c r="I379" t="n">
+        <v>1.0324894317638</v>
+      </c>
+      <c r="J379" t="n">
+        <v>0.03248943176380003</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -9555,6 +14111,18 @@
       <c r="F380" t="n">
         <v>0.08858281172903679</v>
       </c>
+      <c r="G380" t="n">
+        <v>0.0003357060005300273</v>
+      </c>
+      <c r="H380" t="n">
+        <v>0.0003388292436834088</v>
+      </c>
+      <c r="I380" t="n">
+        <v>1.009303507081942</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0.009303507081941879</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -9579,6 +14147,18 @@
       <c r="F381" t="n">
         <v>0.2204002789055841</v>
       </c>
+      <c r="G381" t="n">
+        <v>0.0006715823130209321</v>
+      </c>
+      <c r="H381" t="n">
+        <v>0.0007043940599989007</v>
+      </c>
+      <c r="I381" t="n">
+        <v>1.048857372122226</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0.04885737212222552</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -9603,6 +14183,18 @@
       <c r="F382" t="n">
         <v>0.8706200911312203</v>
       </c>
+      <c r="G382" t="n">
+        <v>0.0005685969281412162</v>
+      </c>
+      <c r="H382" t="n">
+        <v>0.0006499354167085707</v>
+      </c>
+      <c r="I382" t="n">
+        <v>1.143051227577426</v>
+      </c>
+      <c r="J382" t="n">
+        <v>0.143051227577426</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -9627,6 +14219,18 @@
       <c r="F383" t="n">
         <v>0.09314405564608372</v>
       </c>
+      <c r="G383" t="n">
+        <v>0.0004788721558599942</v>
+      </c>
+      <c r="H383" t="n">
+        <v>0.0004842379722050725</v>
+      </c>
+      <c r="I383" t="n">
+        <v>1.011205112428059</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0.01120511242805927</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -9651,6 +14255,18 @@
       <c r="F384" t="n">
         <v>0.03717935333497775</v>
       </c>
+      <c r="G384" t="n">
+        <v>0.0006015013316455175</v>
+      </c>
+      <c r="H384" t="n">
+        <v>0.0006059795338038259</v>
+      </c>
+      <c r="I384" t="n">
+        <v>1.007445041137411</v>
+      </c>
+      <c r="J384" t="n">
+        <v>0.007445041137410969</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -9675,6 +14291,18 @@
       <c r="F385" t="n">
         <v>0.1069681402520788</v>
       </c>
+      <c r="G385" t="n">
+        <v>0.0003284194793950002</v>
+      </c>
+      <c r="H385" t="n">
+        <v>0.0003337090703781608</v>
+      </c>
+      <c r="I385" t="n">
+        <v>1.01610620354464</v>
+      </c>
+      <c r="J385" t="n">
+        <v>0.01610620354464019</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -9699,6 +14327,18 @@
       <c r="F386" t="n">
         <v>-0.005006467745947253</v>
       </c>
+      <c r="G386" t="n">
+        <v>0.0008002403068220133</v>
+      </c>
+      <c r="H386" t="n">
+        <v>0.0008368420687619995</v>
+      </c>
+      <c r="I386" t="n">
+        <v>1.04573846334402</v>
+      </c>
+      <c r="J386" t="n">
+        <v>0.04573846334402026</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -9723,6 +14363,18 @@
       <c r="F387" t="n">
         <v>-0.01082767936042258</v>
       </c>
+      <c r="G387" t="n">
+        <v>0.0007700969861684005</v>
+      </c>
+      <c r="H387" t="n">
+        <v>0.0008044827035645761</v>
+      </c>
+      <c r="I387" t="n">
+        <v>1.044651151755912</v>
+      </c>
+      <c r="J387" t="n">
+        <v>0.04465115175591187</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -9747,6 +14399,18 @@
       <c r="F388" t="n">
         <v>0.1083567793708718</v>
       </c>
+      <c r="G388" t="n">
+        <v>0.0005526458873164924</v>
+      </c>
+      <c r="H388" t="n">
+        <v>0.000561395002652774</v>
+      </c>
+      <c r="I388" t="n">
+        <v>1.0158313226192</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0.01583132261920029</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9771,6 +14435,18 @@
       <c r="F389" t="n">
         <v>0.215531353679895</v>
       </c>
+      <c r="G389" t="n">
+        <v>0.0005068979610700659</v>
+      </c>
+      <c r="H389" t="n">
+        <v>0.0005248777978695485</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1.035470327719463</v>
+      </c>
+      <c r="J389" t="n">
+        <v>0.03547032771946247</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9795,6 +14471,18 @@
       <c r="F390" t="n">
         <v>0.04247305178140955</v>
       </c>
+      <c r="G390" t="n">
+        <v>0.0007473590544221265</v>
+      </c>
+      <c r="H390" t="n">
+        <v>0.0007565948348250201</v>
+      </c>
+      <c r="I390" t="n">
+        <v>1.012357889221045</v>
+      </c>
+      <c r="J390" t="n">
+        <v>0.012357889221045</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9819,6 +14507,18 @@
       <c r="F391" t="n">
         <v>0.05714838673476884</v>
       </c>
+      <c r="G391" t="n">
+        <v>0.0006343929809097898</v>
+      </c>
+      <c r="H391" t="n">
+        <v>0.0006397610680081357</v>
+      </c>
+      <c r="I391" t="n">
+        <v>1.008461769376211</v>
+      </c>
+      <c r="J391" t="n">
+        <v>0.008461769376211284</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9843,6 +14543,18 @@
       <c r="F392" t="n">
         <v>0.06142533427114151</v>
       </c>
+      <c r="G392" t="n">
+        <v>0.000733455961831905</v>
+      </c>
+      <c r="H392" t="n">
+        <v>0.0007446927320255481</v>
+      </c>
+      <c r="I392" t="n">
+        <v>1.015320306573796</v>
+      </c>
+      <c r="J392" t="n">
+        <v>0.01532030657379586</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9867,6 +14579,18 @@
       <c r="F393" t="n">
         <v>0.2317145678808818</v>
       </c>
+      <c r="G393" t="n">
+        <v>0.0006869194700843961</v>
+      </c>
+      <c r="H393" t="n">
+        <v>0.0007354514929801154</v>
+      </c>
+      <c r="I393" t="n">
+        <v>1.070651692096828</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0.07065169209682841</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9891,6 +14615,18 @@
       <c r="F394" t="n">
         <v>0.168266818545002</v>
       </c>
+      <c r="G394" t="n">
+        <v>0.0006554427637897562</v>
+      </c>
+      <c r="H394" t="n">
+        <v>0.0006658943853211315</v>
+      </c>
+      <c r="I394" t="n">
+        <v>1.015945895063276</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0.01594589506327651</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9915,6 +14651,18 @@
       <c r="F395" t="n">
         <v>0.3377944437546446</v>
       </c>
+      <c r="G395" t="n">
+        <v>0.0005900708538028599</v>
+      </c>
+      <c r="H395" t="n">
+        <v>0.0006266331276810957</v>
+      </c>
+      <c r="I395" t="n">
+        <v>1.061962514573633</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0.06196251457363287</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9939,6 +14687,18 @@
       <c r="F396" t="n">
         <v>0.7548244178072095</v>
       </c>
+      <c r="G396" t="n">
+        <v>0.0005947757440054025</v>
+      </c>
+      <c r="H396" t="n">
+        <v>0.0006767546545964138</v>
+      </c>
+      <c r="I396" t="n">
+        <v>1.137831630521682</v>
+      </c>
+      <c r="J396" t="n">
+        <v>0.1378316305216822</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9963,6 +14723,18 @@
       <c r="F397" t="n">
         <v>0.4012575574839302</v>
       </c>
+      <c r="G397" t="n">
+        <v>0.0006501581530227002</v>
+      </c>
+      <c r="H397" t="n">
+        <v>0.0007301098762367992</v>
+      </c>
+      <c r="I397" t="n">
+        <v>1.122972730315523</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0.122972730315523</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9987,6 +14759,18 @@
       <c r="F398" t="n">
         <v>0.3883841879393889</v>
       </c>
+      <c r="G398" t="n">
+        <v>0.0007120665883465395</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0.0007576479725998941</v>
+      </c>
+      <c r="I398" t="n">
+        <v>1.064012811441128</v>
+      </c>
+      <c r="J398" t="n">
+        <v>0.06401281144112844</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -10011,6 +14795,18 @@
       <c r="F399" t="n">
         <v>0.2852900920424444</v>
       </c>
+      <c r="G399" t="n">
+        <v>0.0006813799824726196</v>
+      </c>
+      <c r="H399" t="n">
+        <v>0.0007122788619504776</v>
+      </c>
+      <c r="I399" t="n">
+        <v>1.045347501060613</v>
+      </c>
+      <c r="J399" t="n">
+        <v>0.04534750106061355</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -10035,6 +14831,18 @@
       <c r="F400" t="n">
         <v>0.2027136943968688</v>
       </c>
+      <c r="G400" t="n">
+        <v>0.0005304357258757989</v>
+      </c>
+      <c r="H400" t="n">
+        <v>0.0005526087104197868</v>
+      </c>
+      <c r="I400" t="n">
+        <v>1.04180145390354</v>
+      </c>
+      <c r="J400" t="n">
+        <v>0.04180145390353981</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -10059,6 +14867,18 @@
       <c r="F401" t="n">
         <v>0.4681682224418157</v>
       </c>
+      <c r="G401" t="n">
+        <v>0.0007790817111676792</v>
+      </c>
+      <c r="H401" t="n">
+        <v>0.0008292570125684532</v>
+      </c>
+      <c r="I401" t="n">
+        <v>1.064403130867457</v>
+      </c>
+      <c r="J401" t="n">
+        <v>0.06440313086745664</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -10083,6 +14903,18 @@
       <c r="F402" t="n">
         <v>0.1192292413404487</v>
       </c>
+      <c r="G402" t="n">
+        <v>0.0006611062121619462</v>
+      </c>
+      <c r="H402" t="n">
+        <v>0.0006709840604975759</v>
+      </c>
+      <c r="I402" t="n">
+        <v>1.014941393915098</v>
+      </c>
+      <c r="J402" t="n">
+        <v>0.01494139391509765</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -10107,6 +14939,18 @@
       <c r="F403" t="n">
         <v>0.07294933901456148</v>
       </c>
+      <c r="G403" t="n">
+        <v>0.0006579215071863755</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0.0006905901280338966</v>
+      </c>
+      <c r="I403" t="n">
+        <v>1.049654283209603</v>
+      </c>
+      <c r="J403" t="n">
+        <v>0.04965428320960292</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -10131,6 +14975,18 @@
       <c r="F404" t="n">
         <v>0.2433969517232147</v>
       </c>
+      <c r="G404" t="n">
+        <v>0.0006623179191017963</v>
+      </c>
+      <c r="H404" t="n">
+        <v>0.0006974095360552882</v>
+      </c>
+      <c r="I404" t="n">
+        <v>1.052983040231014</v>
+      </c>
+      <c r="J404" t="n">
+        <v>0.0529830402310139</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -10155,6 +15011,18 @@
       <c r="F405" t="n">
         <v>0.1269605274718159</v>
       </c>
+      <c r="G405" t="n">
+        <v>0.0006728558135649811</v>
+      </c>
+      <c r="H405" t="n">
+        <v>0.0006774349435167017</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1.006805514434748</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0.006805514434748027</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -10179,6 +15047,18 @@
       <c r="F406" t="n">
         <v>0.05219906010508524</v>
       </c>
+      <c r="G406" t="n">
+        <v>0.0005680135814618317</v>
+      </c>
+      <c r="H406" t="n">
+        <v>0.00057270541204268</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1.00826006760045</v>
+      </c>
+      <c r="J406" t="n">
+        <v>0.008260067600449689</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -10203,6 +15083,18 @@
       <c r="F407" t="n">
         <v>0.1005445031569551</v>
       </c>
+      <c r="G407" t="n">
+        <v>0.0007345495145226768</v>
+      </c>
+      <c r="H407" t="n">
+        <v>0.0007500951920174621</v>
+      </c>
+      <c r="I407" t="n">
+        <v>1.021163552881642</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0.02116355288164233</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -10227,6 +15119,18 @@
       <c r="F408" t="n">
         <v>0.08616094349238231</v>
       </c>
+      <c r="G408" t="n">
+        <v>0.0005976276538328894</v>
+      </c>
+      <c r="H408" t="n">
+        <v>0.0006040143706870111</v>
+      </c>
+      <c r="I408" t="n">
+        <v>1.010686782670046</v>
+      </c>
+      <c r="J408" t="n">
+        <v>0.01068678267004618</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -10251,6 +15155,18 @@
       <c r="F409" t="n">
         <v>0.3740543931026775</v>
       </c>
+      <c r="G409" t="n">
+        <v>0.0006389032028672746</v>
+      </c>
+      <c r="H409" t="n">
+        <v>0.0006928052815028378</v>
+      </c>
+      <c r="I409" t="n">
+        <v>1.0843665807178</v>
+      </c>
+      <c r="J409" t="n">
+        <v>0.08436658071780037</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -10275,6 +15191,18 @@
       <c r="F410" t="n">
         <v>2.49745176431641</v>
       </c>
+      <c r="G410" t="n">
+        <v>0.0005295061489366862</v>
+      </c>
+      <c r="H410" t="n">
+        <v>0.0007539080456180415</v>
+      </c>
+      <c r="I410" t="n">
+        <v>1.423794694607385</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0.4237946946073847</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -10299,6 +15227,18 @@
       <c r="F411" t="n">
         <v>0.09473883834121903</v>
       </c>
+      <c r="G411" t="n">
+        <v>0.0007043546094910609</v>
+      </c>
+      <c r="H411" t="n">
+        <v>0.0007173332225480112</v>
+      </c>
+      <c r="I411" t="n">
+        <v>1.018426248486296</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0.01842624848629594</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -10323,6 +15263,18 @@
       <c r="F412" t="n">
         <v>0.2513944686268832</v>
       </c>
+      <c r="G412" t="n">
+        <v>0.0004875720877460962</v>
+      </c>
+      <c r="H412" t="n">
+        <v>0.0004949061811272196</v>
+      </c>
+      <c r="I412" t="n">
+        <v>1.01504206980967</v>
+      </c>
+      <c r="J412" t="n">
+        <v>0.01504206980967009</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -10347,6 +15299,18 @@
       <c r="F413" t="n">
         <v>0.04486104518204907</v>
       </c>
+      <c r="G413" t="n">
+        <v>0.0007392557365231473</v>
+      </c>
+      <c r="H413" t="n">
+        <v>0.0007484415118489141</v>
+      </c>
+      <c r="I413" t="n">
+        <v>1.012425707197037</v>
+      </c>
+      <c r="J413" t="n">
+        <v>0.01242570719703731</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -10371,6 +15335,18 @@
       <c r="F414" t="n">
         <v>0.4660633153419502</v>
       </c>
+      <c r="G414" t="n">
+        <v>0.0005736601407467577</v>
+      </c>
+      <c r="H414" t="n">
+        <v>0.000589584810111781</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.027759762678114</v>
+      </c>
+      <c r="J414" t="n">
+        <v>0.02775976267811374</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -10395,6 +15371,18 @@
       <c r="F415" t="n">
         <v>0.0976718955060509</v>
       </c>
+      <c r="G415" t="n">
+        <v>0.0005700612549159479</v>
+      </c>
+      <c r="H415" t="n">
+        <v>0.0005814896147586685</v>
+      </c>
+      <c r="I415" t="n">
+        <v>1.020047599699449</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0.02004759969944917</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -10419,6 +15407,18 @@
       <c r="F416" t="n">
         <v>0.1489114553272243</v>
       </c>
+      <c r="G416" t="n">
+        <v>0.0005041158292202924</v>
+      </c>
+      <c r="H416" t="n">
+        <v>0.0005081124777081154</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1.007928036090445</v>
+      </c>
+      <c r="J416" t="n">
+        <v>0.007928036090444703</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -10443,6 +15443,18 @@
       <c r="F417" t="n">
         <v>0.1284743592230824</v>
       </c>
+      <c r="G417" t="n">
+        <v>0.0006862792932263172</v>
+      </c>
+      <c r="H417" t="n">
+        <v>0.0007015785334629498</v>
+      </c>
+      <c r="I417" t="n">
+        <v>1.022293023245257</v>
+      </c>
+      <c r="J417" t="n">
+        <v>0.02229302324525673</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -10467,6 +15479,18 @@
       <c r="F418" t="n">
         <v>0.4273943803088786</v>
       </c>
+      <c r="G418" t="n">
+        <v>0.000714367618556981</v>
+      </c>
+      <c r="H418" t="n">
+        <v>0.0007840143296174579</v>
+      </c>
+      <c r="I418" t="n">
+        <v>1.097494216214843</v>
+      </c>
+      <c r="J418" t="n">
+        <v>0.09749421621484317</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -10491,6 +15515,18 @@
       <c r="F419" t="n">
         <v>1.199538842934678</v>
       </c>
+      <c r="G419" t="n">
+        <v>0.0005140977260946757</v>
+      </c>
+      <c r="H419" t="n">
+        <v>0.0006609431767215045</v>
+      </c>
+      <c r="I419" t="n">
+        <v>1.285637230380953</v>
+      </c>
+      <c r="J419" t="n">
+        <v>0.2856372303809526</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -10515,6 +15551,18 @@
       <c r="F420" t="n">
         <v>0.05977827842739528</v>
       </c>
+      <c r="G420" t="n">
+        <v>0.0005061508905295644</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0.0005093874211896716</v>
+      </c>
+      <c r="I420" t="n">
+        <v>1.006394398825854</v>
+      </c>
+      <c r="J420" t="n">
+        <v>0.006394398825854021</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -10539,6 +15587,18 @@
       <c r="F421" t="n">
         <v>0.2070969875663693</v>
       </c>
+      <c r="G421" t="n">
+        <v>0.0007628890231222105</v>
+      </c>
+      <c r="H421" t="n">
+        <v>0.000807408724582502</v>
+      </c>
+      <c r="I421" t="n">
+        <v>1.058356720454686</v>
+      </c>
+      <c r="J421" t="n">
+        <v>0.05835672045468618</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -10563,6 +15623,18 @@
       <c r="F422" t="n">
         <v>0.1804866712711389</v>
       </c>
+      <c r="G422" t="n">
+        <v>0.000714272637297504</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.0007370404941672805</v>
+      </c>
+      <c r="I422" t="n">
+        <v>1.031875583188963</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0.03187558318896281</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -10587,6 +15659,18 @@
       <c r="F423" t="n">
         <v>0.2033223109286891</v>
       </c>
+      <c r="G423" t="n">
+        <v>0.0006482383951445627</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.0006535288678732551</v>
+      </c>
+      <c r="I423" t="n">
+        <v>1.008161307272632</v>
+      </c>
+      <c r="J423" t="n">
+        <v>0.00816130727263179</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -10611,6 +15695,18 @@
       <c r="F424" t="n">
         <v>0.1271762010926376</v>
       </c>
+      <c r="G424" t="n">
+        <v>0.0006606917713128368</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.0006772182533667187</v>
+      </c>
+      <c r="I424" t="n">
+        <v>1.025013906289528</v>
+      </c>
+      <c r="J424" t="n">
+        <v>0.02501390628952858</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -10635,6 +15731,18 @@
       <c r="F425" t="n">
         <v>0.08453554154401419</v>
       </c>
+      <c r="G425" t="n">
+        <v>0.0005467283181853358</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.0005579343061209517</v>
+      </c>
+      <c r="I425" t="n">
+        <v>1.020496446887569</v>
+      </c>
+      <c r="J425" t="n">
+        <v>0.0204964468875693</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -10659,6 +15767,18 @@
       <c r="F426" t="n">
         <v>0.02667830650275202</v>
       </c>
+      <c r="G426" t="n">
+        <v>0.0006153886050734647</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.0006196981616118295</v>
+      </c>
+      <c r="I426" t="n">
+        <v>1.007002983972786</v>
+      </c>
+      <c r="J426" t="n">
+        <v>0.007002983972786392</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -10683,6 +15803,18 @@
       <c r="F427" t="n">
         <v>0.1801056492292991</v>
       </c>
+      <c r="G427" t="n">
+        <v>0.0005376778985179835</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.0005628554621587415</v>
+      </c>
+      <c r="I427" t="n">
+        <v>1.046826480519574</v>
+      </c>
+      <c r="J427" t="n">
+        <v>0.04682648051957432</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -10707,6 +15839,18 @@
       <c r="F428" t="n">
         <v>0.1387386672186972</v>
       </c>
+      <c r="G428" t="n">
+        <v>0.0004325021384263251</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.0004375104058942613</v>
+      </c>
+      <c r="I428" t="n">
+        <v>1.011579751920208</v>
+      </c>
+      <c r="J428" t="n">
+        <v>0.01157975192020783</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -10731,6 +15875,18 @@
       <c r="F429" t="n">
         <v>0.4753895878297961</v>
       </c>
+      <c r="G429" t="n">
+        <v>0.0005494168137312885</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.00056178590768905</v>
+      </c>
+      <c r="I429" t="n">
+        <v>1.022513133287201</v>
+      </c>
+      <c r="J429" t="n">
+        <v>0.02251313328720053</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -10755,6 +15911,18 @@
       <c r="F430" t="n">
         <v>0.09074969764897127</v>
       </c>
+      <c r="G430" t="n">
+        <v>0.0003973013989469291</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.0004017535201636187</v>
+      </c>
+      <c r="I430" t="n">
+        <v>1.011205903700541</v>
+      </c>
+      <c r="J430" t="n">
+        <v>0.01120590370054117</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -10779,6 +15947,18 @@
       <c r="F431" t="n">
         <v>0.06460987233434745</v>
       </c>
+      <c r="G431" t="n">
+        <v>0.0005442970910507024</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.000548355184101078</v>
+      </c>
+      <c r="I431" t="n">
+        <v>1.00745565816371</v>
+      </c>
+      <c r="J431" t="n">
+        <v>0.007455658163709678</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -10803,6 +15983,18 @@
       <c r="F432" t="n">
         <v>0.08966325987472365</v>
       </c>
+      <c r="G432" t="n">
+        <v>0.0004310649895473087</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.0004376188178734479</v>
+      </c>
+      <c r="I432" t="n">
+        <v>1.015203805655899</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0.01520380565589849</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -10827,6 +16019,18 @@
       <c r="F433" t="n">
         <v>0.09651430552949081</v>
       </c>
+      <c r="G433" t="n">
+        <v>0.0006045359216757234</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.0006350457841910696</v>
+      </c>
+      <c r="I433" t="n">
+        <v>1.05046823757102</v>
+      </c>
+      <c r="J433" t="n">
+        <v>0.05046823757102045</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -10851,6 +16055,18 @@
       <c r="F434" t="n">
         <v>0.1093609687876774</v>
       </c>
+      <c r="G434" t="n">
+        <v>0.0004902019247552077</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.0004996809583881118</v>
+      </c>
+      <c r="I434" t="n">
+        <v>1.019336997988406</v>
+      </c>
+      <c r="J434" t="n">
+        <v>0.01933699798840566</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10875,6 +16091,18 @@
       <c r="F435" t="n">
         <v>0.09286460474366011</v>
       </c>
+      <c r="G435" t="n">
+        <v>0.0004259942512311257</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.0004308611371378359</v>
+      </c>
+      <c r="I435" t="n">
+        <v>1.011424768979029</v>
+      </c>
+      <c r="J435" t="n">
+        <v>0.01142476897902936</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10899,6 +16127,18 @@
       <c r="F436" t="n">
         <v>0.1380826250497799</v>
       </c>
+      <c r="G436" t="n">
+        <v>0.0007003137931674918</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.0007553266009765102</v>
+      </c>
+      <c r="I436" t="n">
+        <v>1.078554511342976</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0.07855451134297611</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10923,6 +16163,18 @@
       <c r="F437" t="n">
         <v>0.1259972689647077</v>
       </c>
+      <c r="G437" t="n">
+        <v>0.0006221898956239528</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.0006598840263751525</v>
+      </c>
+      <c r="I437" t="n">
+        <v>1.060583000489583</v>
+      </c>
+      <c r="J437" t="n">
+        <v>0.06058300048958327</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10947,6 +16199,18 @@
       <c r="F438" t="n">
         <v>0.06010924360722964</v>
       </c>
+      <c r="G438" t="n">
+        <v>0.0005008753308026967</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.0005064768688307604</v>
+      </c>
+      <c r="I438" t="n">
+        <v>1.011183497536376</v>
+      </c>
+      <c r="J438" t="n">
+        <v>0.01118349753637659</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10971,6 +16235,18 @@
       <c r="F439" t="n">
         <v>0.2898591651872881</v>
       </c>
+      <c r="G439" t="n">
+        <v>0.0007706823302913666</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.0007916869215158431</v>
+      </c>
+      <c r="I439" t="n">
+        <v>1.027254538477008</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0.02725453847700837</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -10995,6 +16271,18 @@
       <c r="F440" t="n">
         <v>0.5475238051420149</v>
       </c>
+      <c r="G440" t="n">
+        <v>0.0007305360707472791</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.0008220295765476323</v>
+      </c>
+      <c r="I440" t="n">
+        <v>1.125241599236521</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0.1252415992365206</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -11019,6 +16307,18 @@
       <c r="F441" t="n">
         <v>0.03884680181306535</v>
       </c>
+      <c r="G441" t="n">
+        <v>0.0006007404702195874</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.0006048691978808771</v>
+      </c>
+      <c r="I441" t="n">
+        <v>1.006872731014411</v>
+      </c>
+      <c r="J441" t="n">
+        <v>0.006872731014410448</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -11043,6 +16343,18 @@
       <c r="F442" t="n">
         <v>0.1123300302566995</v>
       </c>
+      <c r="G442" t="n">
+        <v>0.0007331224814491588</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.0007593332216453771</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1.035752198110755</v>
+      </c>
+      <c r="J442" t="n">
+        <v>0.03575219811075465</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -11067,6 +16379,18 @@
       <c r="F443" t="n">
         <v>0.2004714101041421</v>
       </c>
+      <c r="G443" t="n">
+        <v>0.000504446660628451</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.0005281096227027394</v>
+      </c>
+      <c r="I443" t="n">
+        <v>1.046908749568901</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0.04690874956890106</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -11091,6 +16415,18 @@
       <c r="F444" t="n">
         <v>0.1607874005857652</v>
       </c>
+      <c r="G444" t="n">
+        <v>0.0005765695067483023</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.0005824943449030156</v>
+      </c>
+      <c r="I444" t="n">
+        <v>1.010276017176364</v>
+      </c>
+      <c r="J444" t="n">
+        <v>0.01027601717636407</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -11115,6 +16451,18 @@
       <c r="F445" t="n">
         <v>0.2895570884449752</v>
       </c>
+      <c r="G445" t="n">
+        <v>0.0007450229153246958</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.00081414518288039</v>
+      </c>
+      <c r="I445" t="n">
+        <v>1.092778713424633</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0.09277871342463249</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -11139,6 +16487,18 @@
       <c r="F446" t="n">
         <v>0.02061819936067579</v>
       </c>
+      <c r="G446" t="n">
+        <v>0.0005708609568615804</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0.0005739457761600064</v>
+      </c>
+      <c r="I446" t="n">
+        <v>1.005403801506036</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0.005403801506036357</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -11163,6 +16523,18 @@
       <c r="F447" t="n">
         <v>0.2052747282817961</v>
       </c>
+      <c r="G447" t="n">
+        <v>0.0005967804178112724</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0.0006368099755116064</v>
+      </c>
+      <c r="I447" t="n">
+        <v>1.067075856555657</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0.067075856555657</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -11187,6 +16559,18 @@
       <c r="F448" t="n">
         <v>0.05994602269537385</v>
       </c>
+      <c r="G448" t="n">
+        <v>0.0006101946895687548</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0.0006161829731447806</v>
+      </c>
+      <c r="I448" t="n">
+        <v>1.009813726140845</v>
+      </c>
+      <c r="J448" t="n">
+        <v>0.009813726140845167</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -11211,6 +16595,18 @@
       <c r="F449" t="n">
         <v>0.4846112407004346</v>
       </c>
+      <c r="G449" t="n">
+        <v>0.0005127762570408214</v>
+      </c>
+      <c r="H449" t="n">
+        <v>0.0005371025151495088</v>
+      </c>
+      <c r="I449" t="n">
+        <v>1.047440297351269</v>
+      </c>
+      <c r="J449" t="n">
+        <v>0.04744029735126915</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -11235,6 +16631,18 @@
       <c r="F450" t="n">
         <v>0.02375882802300417</v>
       </c>
+      <c r="G450" t="n">
+        <v>0.0005851787351398568</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0.0005888250527821174</v>
+      </c>
+      <c r="I450" t="n">
+        <v>1.006231117816318</v>
+      </c>
+      <c r="J450" t="n">
+        <v>0.006231117816318417</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -11259,6 +16667,18 @@
       <c r="F451" t="n">
         <v>0.1129375366420979</v>
       </c>
+      <c r="G451" t="n">
+        <v>0.0006919677624871333</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0.0007331405849531179</v>
+      </c>
+      <c r="I451" t="n">
+        <v>1.059501070278184</v>
+      </c>
+      <c r="J451" t="n">
+        <v>0.05950107027818401</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -11283,6 +16703,18 @@
       <c r="F452" t="n">
         <v>3.488484951988084</v>
       </c>
+      <c r="G452" t="n">
+        <v>0.000813587105225545</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0.0009233688014344511</v>
+      </c>
+      <c r="I452" t="n">
+        <v>1.134935393523072</v>
+      </c>
+      <c r="J452" t="n">
+        <v>0.1349353935230722</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -11307,6 +16739,18 @@
       <c r="F453" t="n">
         <v>4.689265334115936</v>
       </c>
+      <c r="G453" t="n">
+        <v>0.0004294651653817677</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0.000663123932524511</v>
+      </c>
+      <c r="I453" t="n">
+        <v>1.544069195775251</v>
+      </c>
+      <c r="J453" t="n">
+        <v>0.5440691957752507</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -11331,6 +16775,18 @@
       <c r="F454" t="n">
         <v>0.09223484026528478</v>
       </c>
+      <c r="G454" t="n">
+        <v>0.0003343382208193908</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0.0003376443949980676</v>
+      </c>
+      <c r="I454" t="n">
+        <v>1.009888711408986</v>
+      </c>
+      <c r="J454" t="n">
+        <v>0.009888711408986223</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -11355,6 +16811,18 @@
       <c r="F455" t="n">
         <v>0.2139861257892536</v>
       </c>
+      <c r="G455" t="n">
+        <v>0.0004208960159025673</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0.0004293444251796716</v>
+      </c>
+      <c r="I455" t="n">
+        <v>1.020072438222034</v>
+      </c>
+      <c r="J455" t="n">
+        <v>0.02007243822203366</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -11379,6 +16847,18 @@
       <c r="F456" t="n">
         <v>0.1857144227238339</v>
       </c>
+      <c r="G456" t="n">
+        <v>0.0004543871576285581</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0.0004621497361519272</v>
+      </c>
+      <c r="I456" t="n">
+        <v>1.017083622177796</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0.01708362217779639</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -11403,6 +16883,18 @@
       <c r="F457" t="n">
         <v>0.08241531988599037</v>
       </c>
+      <c r="G457" t="n">
+        <v>0.0006232618025513981</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0.0006523674202420336</v>
+      </c>
+      <c r="I457" t="n">
+        <v>1.046698863256962</v>
+      </c>
+      <c r="J457" t="n">
+        <v>0.04669886325696215</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -11427,6 +16919,18 @@
       <c r="F458" t="n">
         <v>0.07128539334522747</v>
       </c>
+      <c r="G458" t="n">
+        <v>0.0005426201591576032</v>
+      </c>
+      <c r="H458" t="n">
+        <v>0.0005496552343320174</v>
+      </c>
+      <c r="I458" t="n">
+        <v>1.012965008866121</v>
+      </c>
+      <c r="J458" t="n">
+        <v>0.01296500886612076</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -11451,6 +16955,18 @@
       <c r="F459" t="n">
         <v>0.08781422984912529</v>
       </c>
+      <c r="G459" t="n">
+        <v>0.0003459988481327677</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0.0003488267065551396</v>
+      </c>
+      <c r="I459" t="n">
+        <v>1.008173028429525</v>
+      </c>
+      <c r="J459" t="n">
+        <v>0.008173028429524753</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -11475,6 +16991,18 @@
       <c r="F460" t="n">
         <v>0.1360579020904698</v>
       </c>
+      <c r="G460" t="n">
+        <v>0.0007176458327568294</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0.0007578142778610649</v>
+      </c>
+      <c r="I460" t="n">
+        <v>1.055972519132354</v>
+      </c>
+      <c r="J460" t="n">
+        <v>0.05597251913235367</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -11499,6 +17027,18 @@
       <c r="F461" t="n">
         <v>0.1216545198558502</v>
       </c>
+      <c r="G461" t="n">
+        <v>0.0006588057849521675</v>
+      </c>
+      <c r="H461" t="n">
+        <v>0.0007003935387270852</v>
+      </c>
+      <c r="I461" t="n">
+        <v>1.063125969329394</v>
+      </c>
+      <c r="J461" t="n">
+        <v>0.06312596932939366</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -11523,6 +17063,18 @@
       <c r="F462" t="n">
         <v>0.1095909245234615</v>
       </c>
+      <c r="G462" t="n">
+        <v>0.0005478652856608679</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0.0005606213013966998</v>
+      </c>
+      <c r="I462" t="n">
+        <v>1.023283124647047</v>
+      </c>
+      <c r="J462" t="n">
+        <v>0.02328312464704673</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -11547,6 +17099,18 @@
       <c r="F463" t="n">
         <v>0.2419580694379628</v>
       </c>
+      <c r="G463" t="n">
+        <v>0.0006771971759204938</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0.0007248610948021098</v>
+      </c>
+      <c r="I463" t="n">
+        <v>1.070384107578163</v>
+      </c>
+      <c r="J463" t="n">
+        <v>0.07038410757816263</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -11571,6 +17135,18 @@
       <c r="F464" t="n">
         <v>0.111510255621896</v>
       </c>
+      <c r="G464" t="n">
+        <v>0.0006855871091299237</v>
+      </c>
+      <c r="H464" t="n">
+        <v>0.0007285955969453632</v>
+      </c>
+      <c r="I464" t="n">
+        <v>1.062732346105546</v>
+      </c>
+      <c r="J464" t="n">
+        <v>0.06273234610554657</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -11595,6 +17171,18 @@
       <c r="F465" t="n">
         <v>0.1269422401976367</v>
       </c>
+      <c r="G465" t="n">
+        <v>0.0005600716274884203</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0.000570290162566931</v>
+      </c>
+      <c r="I465" t="n">
+        <v>1.018245050413167</v>
+      </c>
+      <c r="J465" t="n">
+        <v>0.01824505041316712</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -11619,6 +17207,18 @@
       <c r="F466" t="n">
         <v>0.379422111554574</v>
       </c>
+      <c r="G466" t="n">
+        <v>0.0007006492011734875</v>
+      </c>
+      <c r="H466" t="n">
+        <v>0.0007485259733624155</v>
+      </c>
+      <c r="I466" t="n">
+        <v>1.068332015663104</v>
+      </c>
+      <c r="J466" t="n">
+        <v>0.06833201566310393</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -11643,6 +17243,18 @@
       <c r="F467" t="n">
         <v>0.1202672499057395</v>
       </c>
+      <c r="G467" t="n">
+        <v>0.0005744633548645785</v>
+      </c>
+      <c r="H467" t="n">
+        <v>0.0005765737054563156</v>
+      </c>
+      <c r="I467" t="n">
+        <v>1.003673603501192</v>
+      </c>
+      <c r="J467" t="n">
+        <v>0.003673603501192163</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -11667,6 +17279,18 @@
       <c r="F468" t="n">
         <v>0.2438698076746425</v>
       </c>
+      <c r="G468" t="n">
+        <v>0.0006441308080902862</v>
+      </c>
+      <c r="H468" t="n">
+        <v>0.0006500838057294357</v>
+      </c>
+      <c r="I468" t="n">
+        <v>1.009241907954688</v>
+      </c>
+      <c r="J468" t="n">
+        <v>0.009241907954688426</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -11691,6 +17315,18 @@
       <c r="F469" t="n">
         <v>0.2773707782773366</v>
       </c>
+      <c r="G469" t="n">
+        <v>0.0006085132713409826</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0.0006305721868098135</v>
+      </c>
+      <c r="I469" t="n">
+        <v>1.036250508423949</v>
+      </c>
+      <c r="J469" t="n">
+        <v>0.03625050842394871</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -11715,6 +17351,18 @@
       <c r="F470" t="n">
         <v>0.05202149348778984</v>
       </c>
+      <c r="G470" t="n">
+        <v>0.0004663283122925113</v>
+      </c>
+      <c r="H470" t="n">
+        <v>0.0004698115922097085</v>
+      </c>
+      <c r="I470" t="n">
+        <v>1.007469587038525</v>
+      </c>
+      <c r="J470" t="n">
+        <v>0.007469587038524735</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -11739,6 +17387,18 @@
       <c r="F471" t="n">
         <v>0.1465119794600148</v>
       </c>
+      <c r="G471" t="n">
+        <v>0.0007120906808927818</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0.0007193425903066387</v>
+      </c>
+      <c r="I471" t="n">
+        <v>1.010183968992215</v>
+      </c>
+      <c r="J471" t="n">
+        <v>0.01018396899221441</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -11763,6 +17423,18 @@
       <c r="F472" t="n">
         <v>0.06313972527962557</v>
       </c>
+      <c r="G472" t="n">
+        <v>0.0005313517964912259</v>
+      </c>
+      <c r="H472" t="n">
+        <v>0.0005353850033797261</v>
+      </c>
+      <c r="I472" t="n">
+        <v>1.007590464387499</v>
+      </c>
+      <c r="J472" t="n">
+        <v>0.007590464387498711</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -11787,6 +17459,18 @@
       <c r="F473" t="n">
         <v>0.0942486032528049</v>
       </c>
+      <c r="G473" t="n">
+        <v>0.0005048918908257648</v>
+      </c>
+      <c r="H473" t="n">
+        <v>0.0005079424898638342</v>
+      </c>
+      <c r="I473" t="n">
+        <v>1.006042083648997</v>
+      </c>
+      <c r="J473" t="n">
+        <v>0.006042083648996872</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -11811,6 +17495,18 @@
       <c r="F474" t="n">
         <v>0.2736752185118083</v>
       </c>
+      <c r="G474" t="n">
+        <v>0.0004769168907192476</v>
+      </c>
+      <c r="H474" t="n">
+        <v>0.0004819687867235662</v>
+      </c>
+      <c r="I474" t="n">
+        <v>1.010592822570615</v>
+      </c>
+      <c r="J474" t="n">
+        <v>0.01059282257061535</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -11835,6 +17531,18 @@
       <c r="F475" t="n">
         <v>0.06692342618032905</v>
       </c>
+      <c r="G475" t="n">
+        <v>0.0006251342134528028</v>
+      </c>
+      <c r="H475" t="n">
+        <v>0.0006296809412171558</v>
+      </c>
+      <c r="I475" t="n">
+        <v>1.007273202564358</v>
+      </c>
+      <c r="J475" t="n">
+        <v>0.007273202564358299</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -11859,6 +17567,18 @@
       <c r="F476" t="n">
         <v>0.6001489563368289</v>
       </c>
+      <c r="G476" t="n">
+        <v>0.0006556111594598629</v>
+      </c>
+      <c r="H476" t="n">
+        <v>0.0007446706907714207</v>
+      </c>
+      <c r="I476" t="n">
+        <v>1.135842000287077</v>
+      </c>
+      <c r="J476" t="n">
+        <v>0.1358420002870772</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -11883,6 +17603,18 @@
       <c r="F477" t="n">
         <v>0.1344884661776589</v>
       </c>
+      <c r="G477" t="n">
+        <v>0.0006897857121201649</v>
+      </c>
+      <c r="H477" t="n">
+        <v>0.0007011472715707178</v>
+      </c>
+      <c r="I477" t="n">
+        <v>1.016471143502859</v>
+      </c>
+      <c r="J477" t="n">
+        <v>0.01647114350285887</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -11907,6 +17639,18 @@
       <c r="F478" t="n">
         <v>0.1285940750847735</v>
       </c>
+      <c r="G478" t="n">
+        <v>0.0005626800294931323</v>
+      </c>
+      <c r="H478" t="n">
+        <v>0.0005787745655044473</v>
+      </c>
+      <c r="I478" t="n">
+        <v>1.028603353891577</v>
+      </c>
+      <c r="J478" t="n">
+        <v>0.02860335389157692</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -11931,6 +17675,18 @@
       <c r="F479" t="n">
         <v>0.1236998137988251</v>
       </c>
+      <c r="G479" t="n">
+        <v>0.0008119877180449478</v>
+      </c>
+      <c r="H479" t="n">
+        <v>0.0008361758478881846</v>
+      </c>
+      <c r="I479" t="n">
+        <v>1.029788787817475</v>
+      </c>
+      <c r="J479" t="n">
+        <v>0.02978878781747506</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -11955,6 +17711,18 @@
       <c r="F480" t="n">
         <v>0.4481348962912871</v>
       </c>
+      <c r="G480" t="n">
+        <v>0.00052545077964714</v>
+      </c>
+      <c r="H480" t="n">
+        <v>0.0005706550586431003</v>
+      </c>
+      <c r="I480" t="n">
+        <v>1.086029521216653</v>
+      </c>
+      <c r="J480" t="n">
+        <v>0.08602952121665265</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11979,6 +17747,18 @@
       <c r="F481" t="n">
         <v>0.1147731909966588</v>
       </c>
+      <c r="G481" t="n">
+        <v>0.0006641858008688637</v>
+      </c>
+      <c r="H481" t="n">
+        <v>0.0006755908267342933</v>
+      </c>
+      <c r="I481" t="n">
+        <v>1.017171438851162</v>
+      </c>
+      <c r="J481" t="n">
+        <v>0.0171714388511618</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -12003,6 +17783,18 @@
       <c r="F482" t="n">
         <v>0.0838804576943098</v>
       </c>
+      <c r="G482" t="n">
+        <v>0.0004423965698962997</v>
+      </c>
+      <c r="H482" t="n">
+        <v>0.0004449414030108473</v>
+      </c>
+      <c r="I482" t="n">
+        <v>1.005752379850378</v>
+      </c>
+      <c r="J482" t="n">
+        <v>0.005752379850377663</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -12027,6 +17819,18 @@
       <c r="F483" t="n">
         <v>0.3100101574207081</v>
       </c>
+      <c r="G483" t="n">
+        <v>0.0008008306963281779</v>
+      </c>
+      <c r="H483" t="n">
+        <v>0.000855880176571061</v>
+      </c>
+      <c r="I483" t="n">
+        <v>1.068740472231254</v>
+      </c>
+      <c r="J483" t="n">
+        <v>0.06874047223125417</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -12051,6 +17855,18 @@
       <c r="F484" t="n">
         <v>0.3137774379088419</v>
       </c>
+      <c r="G484" t="n">
+        <v>0.0008037000457727101</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0.0008698962276750435</v>
+      </c>
+      <c r="I484" t="n">
+        <v>1.082364287834138</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0.08236428783413802</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -12075,6 +17891,18 @@
       <c r="F485" t="n">
         <v>0.7950525466015478</v>
       </c>
+      <c r="G485" t="n">
+        <v>0.0007563756415245645</v>
+      </c>
+      <c r="H485" t="n">
+        <v>0.0008448918865734653</v>
+      </c>
+      <c r="I485" t="n">
+        <v>1.117026831893325</v>
+      </c>
+      <c r="J485" t="n">
+        <v>0.1170268318933247</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -12099,6 +17927,18 @@
       <c r="F486" t="n">
         <v>0.04590249288130144</v>
       </c>
+      <c r="G486" t="n">
+        <v>0.0004690671721203221</v>
+      </c>
+      <c r="H486" t="n">
+        <v>0.0004721180158131294</v>
+      </c>
+      <c r="I486" t="n">
+        <v>1.006504065673615</v>
+      </c>
+      <c r="J486" t="n">
+        <v>0.006504065673614895</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -12123,6 +17963,18 @@
       <c r="F487" t="n">
         <v>0.08666859284346018</v>
       </c>
+      <c r="G487" t="n">
+        <v>0.0006657162940196348</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0.0006982928988839113</v>
+      </c>
+      <c r="I487" t="n">
+        <v>1.048934666549285</v>
+      </c>
+      <c r="J487" t="n">
+        <v>0.04893466654928483</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -12147,6 +17999,18 @@
       <c r="F488" t="n">
         <v>0.1244881778857253</v>
       </c>
+      <c r="G488" t="n">
+        <v>0.0006063839390670404</v>
+      </c>
+      <c r="H488" t="n">
+        <v>0.0006381708192772947</v>
+      </c>
+      <c r="I488" t="n">
+        <v>1.05242038609921</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0.05242038609921035</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -12171,6 +18035,18 @@
       <c r="F489" t="n">
         <v>0.1493425835288918</v>
       </c>
+      <c r="G489" t="n">
+        <v>0.0006502121387795828</v>
+      </c>
+      <c r="H489" t="n">
+        <v>0.000686404067972515</v>
+      </c>
+      <c r="I489" t="n">
+        <v>1.05566172489622</v>
+      </c>
+      <c r="J489" t="n">
+        <v>0.05566172489622039</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -12195,6 +18071,18 @@
       <c r="F490" t="n">
         <v>0.06085970411062588</v>
       </c>
+      <c r="G490" t="n">
+        <v>0.0003708206181843232</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0.0003754950193389667</v>
+      </c>
+      <c r="I490" t="n">
+        <v>1.012605558929088</v>
+      </c>
+      <c r="J490" t="n">
+        <v>0.01260555892908831</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -12219,6 +18107,18 @@
       <c r="F491" t="n">
         <v>1.708780784722962</v>
       </c>
+      <c r="G491" t="n">
+        <v>0.0008802366631828689</v>
+      </c>
+      <c r="H491" t="n">
+        <v>0.0009560284552254149</v>
+      </c>
+      <c r="I491" t="n">
+        <v>1.086103880027547</v>
+      </c>
+      <c r="J491" t="n">
+        <v>0.08610388002754694</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -12243,6 +18143,18 @@
       <c r="F492" t="n">
         <v>0.1141915163091944</v>
       </c>
+      <c r="G492" t="n">
+        <v>0.000690334889304005</v>
+      </c>
+      <c r="H492" t="n">
+        <v>0.0007466448411265236</v>
+      </c>
+      <c r="I492" t="n">
+        <v>1.081569036557446</v>
+      </c>
+      <c r="J492" t="n">
+        <v>0.08156903655744557</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -12267,6 +18179,18 @@
       <c r="F493" t="n">
         <v>0.06026968691458699</v>
       </c>
+      <c r="G493" t="n">
+        <v>0.0005890574260405555</v>
+      </c>
+      <c r="H493" t="n">
+        <v>0.0005939735318448053</v>
+      </c>
+      <c r="I493" t="n">
+        <v>1.008345715692431</v>
+      </c>
+      <c r="J493" t="n">
+        <v>0.008345715692431196</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -12291,6 +18215,18 @@
       <c r="F494" t="n">
         <v>0.1362609189661045</v>
       </c>
+      <c r="G494" t="n">
+        <v>0.0006258411867153419</v>
+      </c>
+      <c r="H494" t="n">
+        <v>0.0006652087509081861</v>
+      </c>
+      <c r="I494" t="n">
+        <v>1.062903441046219</v>
+      </c>
+      <c r="J494" t="n">
+        <v>0.06290344104621901</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -12314,6 +18250,18 @@
       </c>
       <c r="F495" t="n">
         <v>0.06673004516809779</v>
+      </c>
+      <c r="G495" t="n">
+        <v>0.0006776833233060721</v>
+      </c>
+      <c r="H495" t="n">
+        <v>0.0006827894208929838</v>
+      </c>
+      <c r="I495" t="n">
+        <v>1.007534636623492</v>
+      </c>
+      <c r="J495" t="n">
+        <v>0.007534636623491996</v>
       </c>
     </row>
   </sheetData>
